--- a/naver-place-crawler/results_nail/옹진군_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/옹진군_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>라비쥬</t>
+          <t>쏘니네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sincity01@naver.com</t>
+          <t>ultramariine@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1340-8384</t>
+          <t>0507-1485-3336</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 15 세영프라자 4층</t>
+          <t>인천광역시 중구 흰바위로 284 110-1호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://instagram.com/salon_labijou</t>
+          <t>https://www.instagram.com/ssoninail</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>332</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="n">
-        <v>403</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>735</v>
+        <v>13</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>37064341</t>
+          <t>1226536825</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37064341</t>
+          <t>https://m.place.naver.com/place/1226536825</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,25 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>온리원네일</t>
+          <t>도도네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nail_one@naver.com</t>
+          <t>dutjdgml70@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1405-5840</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로248번길 28-4 1층 102호</t>
+          <t>인천광역시 중구 두미포로 89 102호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__only_one__nail</t>
+          <t>http://www.instagram.com/dodonail.2024</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>244</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2039624196</t>
+          <t>38321738</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039624196</t>
+          <t>https://m.place.naver.com/place/38321738</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -748,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>언니네일 페디베네 영종 운서점</t>
+          <t>네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>botong56@naver.com</t>
+          <t>vizarai@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1416-6632</t>
+          <t>0507-1327-8743</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 중구 넙디로 47 백산빌딩 103호 언니네일 페디베네 영종 운서점</t>
+          <t>인천광역시 중구 하늘중앙로195번길 14 301호 네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/botong56</t>
+          <t>https://blog.naver.com/vizarai</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>37101621</t>
+          <t>1976884898</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37101621</t>
+          <t>https://m.place.naver.com/place/1976884898</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>퐁네일</t>
+          <t>언니네일 페디베네 영종 운서점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>yegi1929@naver.com</t>
+          <t>botong56@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1340-7654</t>
+          <t>0507-1416-6632</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 90-7 스카이에비뉴1 (6층)아띠스윤 내</t>
+          <t>인천광역시 중구 넙디로 47 백산빌딩 103호 언니네일 페디베네 영종 운서점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_pongnail</t>
+          <t>https://blog.naver.com/botong56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -879,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="Q5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="R5" t="n">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1591123938</t>
+          <t>37101621</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591123938</t>
+          <t>https://m.place.naver.com/place/37101621</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -936,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일했냥</t>
+          <t>네일공간 영종하늘도시점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nababa33@naver.com</t>
+          <t>juseul2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1346-6543</t>
+          <t>0507-1357-2207</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 90-27 109호</t>
+          <t>인천광역시 중구 하늘달빛로 95 102동 108호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_PxiixmG</t>
+          <t>https://www.instagram.com/nail_gonggan1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -984,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1506</v>
+        <v>24</v>
       </c>
       <c r="Q6" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="R6" t="n">
-        <v>1571</v>
+        <v>33</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1874909116</t>
+          <t>2006802771</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874909116</t>
+          <t>https://m.place.naver.com/place/2006802771</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오니네일</t>
+          <t>N.Nail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wjsska1907@naver.com</t>
+          <t>nailon22@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1311-0663</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 갑룡길 29 1층, 카페88 내부위치</t>
+          <t>인천광역시 중구 햇내로13번길 8 207호(운서동, 프라임시티3)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://instagram.com/oninail_</t>
+          <t>https://www.instagram.com/n.nail_3/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1245994155</t>
+          <t>2001565256</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245994155</t>
+          <t>https://m.place.naver.com/place/2001565256</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1124,25 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>라르떼네일</t>
+          <t>라비쥬</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>limkyungmi10@naver.com</t>
+          <t>sincity01@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1340-8384</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 11 해솔프라자 403-1호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 15 세영프라자 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rarete_nail02</t>
+          <t>http://instagram.com/salon_labijou</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>53</v>
+        <v>332</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>403</v>
       </c>
       <c r="R8" t="n">
-        <v>70</v>
+        <v>735</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1844112944</t>
+          <t>37064341</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1844112944</t>
+          <t>https://m.place.naver.com/place/37064341</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>루시네일</t>
+          <t>퍼플리네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hyeoniizzang@naver.com</t>
+          <t>u_un0709@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1321-0922</t>
+          <t>0507-1315-4140</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 40 비젼프라자2 509호</t>
+          <t>인천광역시 강화군 선원면 중앙로 162-3 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lllucynail_</t>
+          <t>https://www.instagram.com/purply._.nail/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1271,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>691165364</t>
+          <t>2094549338</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/691165364</t>
+          <t>https://m.place.naver.com/place/2094549338</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>태봉씨뷰티살롱&amp;LCN공식 인증매장</t>
+          <t>주드네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>xogns07@naver.com</t>
+          <t>luv_gayeon0@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1330-1831</t>
+          <t>0507-1397-7996</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 20 9층 910호</t>
+          <t>인천광역시 중구 하늘중앙로225번길 3 영종M타워 2층 201호 이철헤어커커 안</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xogns07</t>
+          <t>https://blog.naver.com/luv_gayeon0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="Q10" t="n">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="R10" t="n">
-        <v>568</v>
+        <v>481</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1381683377</t>
+          <t>1740443365</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381683377</t>
+          <t>https://m.place.naver.com/place/1740443365</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1406,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>원네일앤뷰티 영종하늘도시점</t>
+          <t>네일,빛</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wonnail0929@naver.com</t>
+          <t>ekeor0718@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1415,12 +1419,12 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 70 메디피아빌딩 304호</t>
+          <t>인천광역시 중구 하늘중앙로 193 조양타워 4층 409호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wonnail0929</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1430,12 +1434,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1451,17 +1455,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>214</v>
+        <v>109</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1259164731</t>
+          <t>1646288604</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259164731</t>
+          <t>https://m.place.naver.com/place/1646288604</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1492,29 +1496,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
+          <t>압구정네일샵</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>vizarai@naver.com</t>
+          <t>bitna0614@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1327-8743</t>
+          <t>032-751-0401</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 14 301호 네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
+          <t>인천광역시 중구 운남로 158 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vizarai</t>
+          <t>https://www.instagram.com/agn0401/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1529,7 +1533,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1549,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>242</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1976884898</t>
+          <t>414262111</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976884898</t>
+          <t>https://m.place.naver.com/place/414262111</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1586,34 +1590,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>슈가네일</t>
+          <t>레푸스 강화점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sugar_nail@naver.com</t>
+          <t>refuss_ganghwa@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1406-0391</t>
+          <t>0507-1409-2278</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 36 영종주공스카이빌아파트 상가 103호</t>
+          <t>인천광역시 강화군 강화읍 충렬사로 25 남산빌딩 2층 202호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xlLxmyn</t>
+          <t>https://www.youtube.com/@강화레푸스</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1623,7 +1627,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1634,7 +1638,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1643,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1533004146</t>
+          <t>1506333714</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533004146</t>
+          <t>https://m.place.naver.com/place/1506333714</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1680,29 +1684,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>퍼플리네일</t>
+          <t>네일바이에스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>u_un0709@naver.com</t>
+          <t>nufine@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1315-4140</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 선원면 중앙로 162-3 2층</t>
+          <t>인천광역시 중구 햇내로안길 14-5 102호 네일바이에스</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/purply._.nail/</t>
+          <t>https://www.instagram.com/nailby_s</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>39</v>
+        <v>337</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,17 +1752,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2094549338</t>
+          <t>1163668428</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094549338</t>
+          <t>https://m.place.naver.com/place/1163668428</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1774,29 +1774,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>바비수네일&amp;태닝</t>
+          <t>태봉씨뷰티살롱&amp;LCN공식 인증매장</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vavisu_nail@naver.com</t>
+          <t>xogns07@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>032-752-8700</t>
+          <t>0507-1330-1831</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 94 스타타워 407호</t>
+          <t>인천광역시 중구 하늘중앙로225번길 20 9층 910호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vavisu_nail</t>
+          <t>https://blog.naver.com/xogns07</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>455</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="R15" t="n">
-        <v>13</v>
+        <v>568</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1846,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>35516411</t>
+          <t>1381683377</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35516411</t>
+          <t>https://m.place.naver.com/place/1381683377</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1868,29 +1868,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>플레이버네일</t>
+          <t>네일핫플</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>oao08@naver.com</t>
+          <t>dydals1wj@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1382-0428</t>
+          <t>032-747-0321</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 중구 운서로7번길 60 1층 103호</t>
+          <t>인천광역시 중구 자연대로 38 208호 네일핫플</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flavornail?igsh=MWgwY3luaWppNHdtZg%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_hotple?igsh=MTl4dmd6ZGdlcHF4dA==</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1916,7 +1916,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,17 +1940,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1693860525</t>
+          <t>1813910551</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693860525</t>
+          <t>https://m.place.naver.com/place/1813910551</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1962,29 +1962,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>버디네일</t>
+          <t>네일파르크</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hhj6910@naver.com</t>
+          <t>liphop2588@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1420-9856</t>
+          <t>0507-1385-0712</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디칼 3층 309호</t>
+          <t>인천광역시 중구 화랑목로 50-7 102호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buddy_nail__</t>
+          <t>http://www.instagram.com/nail_parc</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>620</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R17" t="n">
-        <v>622</v>
+        <v>22</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2034,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1255393282</t>
+          <t>1965314720</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1255393282</t>
+          <t>https://m.place.naver.com/place/1965314720</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2056,29 +2056,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>두손네일</t>
+          <t>네일바유</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>doosonnail@naver.com</t>
+          <t>fhwmay@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1401-4970</t>
+          <t>0507-1414-0777</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 31 에어로시티</t>
+          <t>인천광역시 중구 흰바위로 258 센타프라자 2층 208호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jangjeongsnyi/</t>
+          <t>https://www.instagram.com/nail._.bayu</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2113,13 +2113,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7</v>
+        <v>288</v>
       </c>
       <c r="Q18" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>69</v>
+        <v>293</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2128,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>125000879</t>
+          <t>1489158637</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/125000879</t>
+          <t>https://m.place.naver.com/place/1489158637</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>달빛네일</t>
+          <t>더예쁨네일피부</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>wltjsk12@naver.com</t>
+          <t>tlsrl0104@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2163,22 +2163,22 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 94 스타타워1 107호</t>
+          <t>인천광역시 중구 자연대로 37 스카이가든 2층 206호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moonlight.nail_2024?igsh=ODhycnVmMG9nc3R0</t>
+          <t>https://www.theyepm.com</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2218,17 +2218,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1390289802</t>
+          <t>2044624904</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1390289802</t>
+          <t>https://m.place.naver.com/place/2044624904</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2240,29 +2240,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>템팅네일</t>
+          <t>옥스네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>diet_wonna@naver.com</t>
+          <t>odiyablog@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1398-4155</t>
+          <t>0507-1434-0166</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로안길 18-4 1층</t>
+          <t>인천광역시 중구 하늘달빛로 139 777동(센텀베뉴 정문상가내) 103-2호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tempting_nail</t>
+          <t>https://www.instagram.com/ok_s_nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>278</v>
+        <v>134</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="R20" t="n">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,17 +2312,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1951261120</t>
+          <t>2011391847</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1951261120</t>
+          <t>https://m.place.naver.com/place/2011391847</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2334,29 +2334,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일 또 보니</t>
+          <t>아하뷰티샵</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>yellowground_@naver.com</t>
+          <t>ahasoft_crm@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1355-4749</t>
+          <t>0507-1366-0805</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 18 효정타워 305호</t>
+          <t>인천광역시 옹진군 북도면 장봉로238번길 66</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ddoboni</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>326</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>336</v>
+        <v>1</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,17 +2406,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1350394025</t>
+          <t>1135765422</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350394025</t>
+          <t>https://m.place.naver.com/place/1135765422</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2428,29 +2428,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>블라썸뷰티 동성제약 풀리메디 영종점</t>
+          <t>네일917</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>yanstar80@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1303-3553</t>
+          <t>032-751-0917</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 중구 모랫말로 6-9 101호</t>
+          <t>인천광역시 중구 화랑목로100번길 75 104호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://instagram.com/blossom_btl</t>
+          <t>http://www.instagram.com/nail.917</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>406</v>
+        <v>438</v>
       </c>
       <c r="Q22" t="n">
-        <v>475</v>
+        <v>10</v>
       </c>
       <c r="R22" t="n">
-        <v>881</v>
+        <v>448</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,17 +2500,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1867109358</t>
+          <t>1363080406</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867109358</t>
+          <t>https://m.place.naver.com/place/1363080406</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2522,29 +2522,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>쏘니네일</t>
+          <t>네일이안</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ultramariine@naver.com</t>
+          <t>wjstngusrn@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1485-3336</t>
+          <t>0507-1467-1252</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 284 110-1호</t>
+          <t>인천광역시 중구 자연대로 47 610호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssoninail</t>
+          <t>https://www.instagram.com/nail_ian</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2579,13 +2579,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="R23" t="n">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2594,17 +2594,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1226536825</t>
+          <t>1117993147</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226536825</t>
+          <t>https://m.place.naver.com/place/1117993147</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2616,29 +2616,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>젤리쉬네일</t>
+          <t>네일 그대와</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>thswltn011@naver.com</t>
+          <t>dodo1052@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1333-9838</t>
+          <t>0507-1379-0491</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로 166 솔리움센텀스카이 상가 1층 107호 젤리쉬네일</t>
+          <t>인천광역시 중구 하늘달빛로 94 스타 타워1 507호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gelish._.nail_</t>
+          <t>https://www.instagram.com/nail._.withyou</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2673,13 +2673,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1279</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="R24" t="n">
-        <v>1314</v>
+        <v>23</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,17 +2688,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1825609603</t>
+          <t>1267766371</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1825609603</t>
+          <t>https://m.place.naver.com/place/1267766371</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2710,29 +2710,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>네일유희 하늘도시</t>
+          <t>플레이버네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kim960113@naver.com</t>
+          <t>oao08@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1492-3774</t>
+          <t>0507-1382-0428</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 중구 월촌길 28 102호 네일유희</t>
+          <t>인천광역시 중구 운서로7번길 60 1층 103호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailyuhee</t>
+          <t>https://www.instagram.com/flavornail?igsh=MWgwY3luaWppNHdtZg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>80</v>
+        <v>255</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>87</v>
+        <v>258</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2782,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1310153514</t>
+          <t>1693860525</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310153514</t>
+          <t>https://m.place.naver.com/place/1693860525</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2804,29 +2804,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>스튜디오공감</t>
+          <t>바비수네일&amp;태닝</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>studi5gonggam_art@naver.com</t>
+          <t>vavisu_nail@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1380-0311</t>
+          <t>032-752-8700</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호 스튜디오공감</t>
+          <t>인천광역시 중구 하늘달빛로 94 스타타워 407호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/studi5gonggam_art</t>
+          <t>https://blog.naver.com/vavisu_nail</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2857,18 +2857,18 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>206</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
+        <v>10</v>
+      </c>
+      <c r="R26" t="n">
         <v>13</v>
       </c>
-      <c r="R26" t="n">
-        <v>219</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>X</t>
@@ -2876,17 +2876,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1085588496</t>
+          <t>35516411</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1085588496</t>
+          <t>https://m.place.naver.com/place/35516411</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2898,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>그때 그 네일</t>
+          <t>오앤오네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>goodbyealice@naver.com</t>
+          <t>bliss-mj@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1301-9627</t>
+          <t>0507-1319-2481</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호</t>
+          <t>인천광역시 중구 하늘달빛로 88 7층 701호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ggnail</t>
+          <t>https://www.instagram.com/ono__nail_studio</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +2970,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1380919881</t>
+          <t>2034560142</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1380919881</t>
+          <t>https://m.place.naver.com/place/2034560142</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2992,29 +2992,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>더리온</t>
+          <t>네일했냥</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jhjy101526@naver.com</t>
+          <t>mementomori-24@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>032-836-4667</t>
+          <t>0507-1346-6543</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 옹진군 백령면 백령로 282 더리온</t>
+          <t>인천광역시 중구 하늘달빛로 90-27 109호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rPaGn</t>
+          <t>http://pf.kakao.com/_PxiixmG</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3045,17 +3045,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>41</v>
+        <v>1515</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="R28" t="n">
-        <v>43</v>
+        <v>1581</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3064,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1040252234</t>
+          <t>1874909116</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040252234</t>
+          <t>https://m.place.naver.com/place/1874909116</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3086,25 +3086,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일,빛</t>
+          <t>아이온네일 인천영종점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ekeor0718@naver.com</t>
+          <t>ym6030@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1329-3883</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 193 조양타워 4층 409호</t>
+          <t>인천광역시 중구 영종대로196번길 15-25 운서역반도유보라퍼스트지 상가동2층226호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ym6030</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3114,12 +3118,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3135,17 +3139,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>103</v>
+        <v>883</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="R29" t="n">
-        <v>108</v>
+        <v>955</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3154,17 +3158,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1646288604</t>
+          <t>1792903749</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1646288604</t>
+          <t>https://m.place.naver.com/place/1792903749</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3176,29 +3180,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일 바이 담</t>
+          <t>스튜디오공감</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>flowerhyodol@naver.com</t>
+          <t>studi5gonggam_art@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>032-751-6686</t>
+          <t>0507-1380-0311</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 17 프라임시티1차 102호 네일바이담</t>
+          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호 스튜디오공감</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailby.dam</t>
+          <t>https://blog.naver.com/studi5gonggam_art</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3213,7 +3217,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3233,13 +3237,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R30" t="n">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,17 +3252,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1880192448</t>
+          <t>1085588496</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880192448</t>
+          <t>https://m.place.naver.com/place/1085588496</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3270,39 +3274,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>미뇽네일</t>
+          <t>네일더스킨</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>akstjd1018@naver.com</t>
+          <t>feel3051@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1381-9702</t>
+          <t>0507-1411-0441</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 347-1 101호</t>
+          <t>인천광역시 중구 흰바위로 258 211호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hkxiqG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3318,22 +3322,22 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3342,17 +3346,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1280952259</t>
+          <t>1314782883</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280952259</t>
+          <t>https://m.place.naver.com/place/1314782883</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3364,29 +3368,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>주드네일</t>
+          <t>소소네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>luv_gayeon0@naver.com</t>
+          <t>iamkimz@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1397-7996</t>
+          <t>0507-1327-9628</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 3 영종M타워 2층 201호 이철헤어커커 안</t>
+          <t>인천광역시 강화군 강화읍 강화대로404번길 9 2층 윈썸헤어&amp;소소네일</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/luv_gayeon0</t>
+          <t>https://www.instagram.com/sosonail_y?igsh=djM3NzVmbHM5eDRo&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3401,7 +3405,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3421,13 +3425,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>478</v>
+        <v>1</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3436,17 +3440,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1740443365</t>
+          <t>1958174820</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1740443365</t>
+          <t>https://m.place.naver.com/place/1958174820</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3458,29 +3462,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비너스네일앤뷰티</t>
+          <t>두손네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>doosonnail@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1309-4148</t>
+          <t>0507-1401-4970</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 신문길 42 2층</t>
+          <t>인천광역시 중구 흰바위로 31 에어로시티</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/venus_nail4148</t>
+          <t>https://www.instagram.com/jangjeongsnyi/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3515,13 +3519,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R33" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3530,17 +3534,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1141156599</t>
+          <t>125000879</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141156599</t>
+          <t>https://m.place.naver.com/place/125000879</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3552,29 +3556,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일바유</t>
+          <t>가디스뷰티샵</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>fhwmay@naver.com</t>
+          <t>goddess503@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1414-0777</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 258 센타프라자 2층 208호</t>
+          <t>인천광역시 중구 하늘별빛로65번길 7-9 스카이타워5층 503호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.bayu</t>
+          <t>https://blog.naver.com/goddess503</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3609,13 +3609,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>285</v>
+        <v>44</v>
       </c>
       <c r="Q34" t="n">
         <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>290</v>
+        <v>49</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3624,17 +3624,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1489158637</t>
+          <t>1848560502</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1489158637</t>
+          <t>https://m.place.naver.com/place/1848560502</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3646,29 +3646,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일더스킨</t>
+          <t>오니네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feel3051@naver.com</t>
+          <t>wjsska1907@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1411-0441</t>
+          <t>0507-1311-0663</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 258 211호</t>
+          <t>인천광역시 강화군 강화읍 갑룡길 29 1층, 카페88 내부위치</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/oninail_</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3699,17 +3699,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3718,17 +3718,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1314782883</t>
+          <t>1245994155</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314782883</t>
+          <t>https://m.place.naver.com/place/1245994155</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3740,29 +3740,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일공간 영종하늘도시점</t>
+          <t>레푸스 인천영종점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>juseul2@naver.com</t>
+          <t>lje9539@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1357-2207</t>
+          <t>0507-1497-0007</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 95 102동 108호</t>
+          <t>인천광역시 중구 영종대로 100 신성하우스빌 3층 301호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_gonggan1</t>
+          <t>https://www.instagram.com/nail_heyazi/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="Q36" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="R36" t="n">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3812,17 +3812,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2006802771</t>
+          <t>1131150431</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2006802771</t>
+          <t>https://m.place.naver.com/place/1131150431</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3834,29 +3834,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>소소네일</t>
+          <t>오늘네일샵</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>iamkimz@naver.com</t>
+          <t>webmaia21@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0507-1327-9628</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로404번길 9 2층 윈썸헤어&amp;소소네일</t>
+          <t>충청남도 서산시 대산읍 충의로 1889</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sosonail_y?igsh=djM3NzVmbHM5eDRo&amp;utm_source=qr</t>
+          <t>http://instagram.com/_nail_2day</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3891,10 +3887,10 @@
         </is>
       </c>
       <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
         <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -3906,17 +3902,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1958174820</t>
+          <t>1283160281</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958174820</t>
+          <t>https://m.place.naver.com/place/1283160281</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3928,29 +3924,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>네일핫플</t>
+          <t>그레이스네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dydals1wj@naver.com</t>
+          <t>lumirode@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>032-747-0321</t>
+          <t>0507-1379-5084</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 38 208호 네일핫플</t>
+          <t>인천광역시 강화군 강화읍 강화대로248번길 24 갑룡프라자 2층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hotple?igsh=MTl4dmd6ZGdlcHF4dA==</t>
+          <t>https://www.instagram.com/grace_nail_?igsh=eGhhYXZlaGl0Z3hh&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3976,7 +3972,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3985,13 +3981,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4000,17 +3996,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1813910551</t>
+          <t>1030374689</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1813910551</t>
+          <t>https://m.place.naver.com/place/1030374689</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4022,29 +4018,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일, 피어나</t>
+          <t>라르떼네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bbang52@naver.com</t>
+          <t>limkyungmi10@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1365-4941</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 193 314호</t>
+          <t>인천광역시 중구 하늘별빛로65번길 11 해솔프라자 403-1호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fe_ar_not/</t>
+          <t>https://www.instagram.com/rarete_nail02</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4079,13 +4071,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R39" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4094,17 +4086,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1581968497</t>
+          <t>1844112944</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581968497</t>
+          <t>https://m.place.naver.com/place/1844112944</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4116,34 +4108,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>지니네일</t>
+          <t>미뇽네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>goto_seoul@naver.com</t>
+          <t>akstjd1018@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1316-6480</t>
+          <t>0507-1381-9702</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 남문안길32번길 8 2층</t>
+          <t>인천광역시 강화군 강화읍 강화대로 347-1 101호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/jineenail</t>
+          <t>http://pf.kakao.com/_hkxiqG</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4164,7 +4156,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4173,13 +4165,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="Q40" t="n">
         <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4188,17 +4180,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1155579596</t>
+          <t>1280952259</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155579596</t>
+          <t>https://m.place.naver.com/place/1280952259</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4210,29 +4202,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>엔샵</t>
+          <t>제이네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jiansritual@naver.com</t>
+          <t>rhkdmswl@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1404-6421</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 19 센타프라자 203호</t>
+          <t>인천광역시 강화군 강화읍 향나무길28번길 13-1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jiansritual</t>
+          <t>https://www.instagram.com/j.nail_shop</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4247,7 +4235,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4267,13 +4255,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4282,17 +4270,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>34362707</t>
+          <t>1237271418</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34362707</t>
+          <t>https://m.place.naver.com/place/1237271418</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4304,29 +4292,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아하뷰티샵</t>
+          <t>네일오다</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ahasoft_crm@naver.com</t>
+          <t>jin568900@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0507-1366-0805</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 옹진군 북도면 장봉로238번길 66</t>
+          <t>인천광역시 중구 자연대로 28 그랑블루인영종 209호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.oda</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4336,7 +4320,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4357,17 +4341,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4376,17 +4360,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1135765422</t>
+          <t>1153727265</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135765422</t>
+          <t>https://m.place.naver.com/place/1153727265</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4398,25 +4382,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일은영</t>
+          <t>루시네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>naileun_0@naver.com</t>
+          <t>hyeoniizzang@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1321-0922</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 45 118호</t>
+          <t>인천광역시 중구 자연대로 40 비젼프라자2 509호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://instagram.com/naileun_0</t>
+          <t>https://www.instagram.com/lllucynail_</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4451,13 +4439,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>379</v>
+        <v>3</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4466,17 +4454,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1430851204</t>
+          <t>691165364</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430851204</t>
+          <t>https://m.place.naver.com/place/691165364</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4476,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>제이네일</t>
+          <t>네일은영</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>morningapple6@naver.com</t>
+          <t>naileun_0@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4501,12 +4489,12 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 향나무길28번길 13-1</t>
+          <t>인천광역시 중구 흰바위로 45 118호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j.nail_shop</t>
+          <t>http://instagram.com/naileun_0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4541,13 +4529,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>5</v>
+        <v>376</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R44" t="n">
-        <v>7</v>
+        <v>382</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,17 +4544,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1237271418</t>
+          <t>1430851204</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237271418</t>
+          <t>https://m.place.naver.com/place/1430851204</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4578,29 +4566,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>더 트윙클 네일</t>
+          <t>그리닷뷰티</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>doll_a_wh@naver.com</t>
+          <t>dean0707@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1488-2043</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 262 럭키프라자 305호</t>
+          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the.twinkle_nail1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4610,7 +4594,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4631,17 +4615,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>412</v>
+        <v>34</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>418</v>
+        <v>34</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,17 +4634,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1809066919</t>
+          <t>1208135114</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1809066919</t>
+          <t>https://m.place.naver.com/place/1208135114</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4672,25 +4656,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>가디스뷰티샵</t>
+          <t>네일위클로</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>goddess503@naver.com</t>
+          <t>summerstar1984@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1368-4179</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 7-9 스카이타워5층 503호</t>
+          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goddess503</t>
+          <t>https://www.instagram.com/nail.weclo</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4705,7 +4693,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4725,13 +4713,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,17 +4728,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1848560502</t>
+          <t>2038322752</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1848560502</t>
+          <t>https://m.place.naver.com/place/2038322752</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4762,25 +4750,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>N.Nail</t>
+          <t>네일은빛나</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>nailon22@naver.com</t>
+          <t>raronail@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1375-7181</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 8 207호(운서동, 프라임시티3)</t>
+          <t>인천광역시 중구 영종대로196번길 15-25 반도유보라퍼스티지 상가동 1층 109호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.nail_3/</t>
+          <t>https://www.instagram.com/nail_by_shine</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4815,13 +4807,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4830,17 +4822,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2001565256</t>
+          <t>1399161803</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001565256</t>
+          <t>https://m.place.naver.com/place/1399161803</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4852,30 +4844,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>더예쁨네일피부</t>
+          <t>루비네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>tlsrl0104@naver.com</t>
+          <t>ruby1004_mj@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1342-4252</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 37 스카이가든 2층 206호</t>
+          <t>인천광역시 강화군 강화읍 중앙로 68 하나로마트 2층 214호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.theyepm.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4901,17 +4897,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4920,17 +4916,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2044624904</t>
+          <t>1791159276</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044624904</t>
+          <t>https://m.place.naver.com/place/1791159276</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4942,29 +4938,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>루비네일</t>
+          <t>원네일앤뷰티 영종하늘도시점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ruby1004_mj@naver.com</t>
+          <t>wonnail0929@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1342-4252</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 중앙로 68 하나로마트 2층 214호</t>
+          <t>인천광역시 중구 하늘달빛로 70 메디피아빌딩 304호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wonnail0929</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4974,12 +4966,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4995,17 +4987,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>14</v>
+        <v>196</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R49" t="n">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5014,17 +5006,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1791159276</t>
+          <t>1259164731</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1791159276</t>
+          <t>https://m.place.naver.com/place/1259164731</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5036,25 +5028,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일바이에스</t>
+          <t>네일 또 보니</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nufine@naver.com</t>
+          <t>to_nail@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1355-4749</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로안길 14-5 102호 네일바이에스</t>
+          <t>인천광역시 중구 하늘중앙로195번길 18 효정타워 305호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailby_s</t>
+          <t>https://www.instagram.com/nail_ddoboni</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5089,14 +5085,14 @@
         </is>
       </c>
       <c r="P50" t="n">
+        <v>327</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>10</v>
+      </c>
+      <c r="R50" t="n">
         <v>337</v>
       </c>
-      <c r="Q50" t="n">
-        <v>3</v>
-      </c>
-      <c r="R50" t="n">
-        <v>340</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>X</t>
@@ -5104,17 +5100,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1163668428</t>
+          <t>1350394025</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163668428</t>
+          <t>https://m.place.naver.com/place/1350394025</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5126,34 +5122,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일파르크</t>
+          <t>그때 그 네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>paigethos@naver.com</t>
+          <t>goodbyealice@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1385-0712</t>
+          <t>0507-1301-9627</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 중구 화랑목로 50-7 102호</t>
+          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_parc</t>
+          <t>https://www.instagram.com/_ggnail</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5163,7 +5159,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5183,13 +5179,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="R51" t="n">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5198,17 +5194,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1965314720</t>
+          <t>1380919881</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965314720</t>
+          <t>https://m.place.naver.com/place/1380919881</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5220,29 +5216,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일위클로</t>
+          <t>블랑디에 네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>summerstar1984@naver.com</t>
+          <t>gkgmlwn2929@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1368-4179</t>
+          <t>0507-1393-2128</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
+          <t>인천광역시 중구 하늘별빛로65번길 7-15 디에스지타워 10층 1003호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.weclo?igsh=ZjlpdGtuZ2gzemRy&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/blancdrenail</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5268,7 +5264,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5277,13 +5273,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>41</v>
+        <v>302</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5292,17 +5288,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2038322752</t>
+          <t>1984068599</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038322752</t>
+          <t>https://m.place.naver.com/place/1984068599</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5314,30 +5310,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일오다</t>
+          <t>더네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jin568900@naver.com</t>
+          <t>thenail_@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1481-0271</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 28 그랑블루인영종 209호</t>
+          <t>인천광역시 중구 하늘중앙로225번길 20 215호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.oda</t>
+          <t>https://www.instagram.com/p/Cf_KCSIrY34/?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5367,13 +5367,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>197</v>
+        <v>17</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>240</v>
+        <v>23</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1153727265</t>
+          <t>1979788121</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153727265</t>
+          <t>https://m.place.naver.com/place/1979788121</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5404,29 +5404,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>압구정네일샵</t>
+          <t>달빛네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>daynote@naver.com</t>
+          <t>duoshan_sz@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>032-751-0401</t>
+          <t>0507-1316-8875</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 중구 운남로 158 2층</t>
+          <t>인천광역시 강화군 강화읍 강화대로 310 201호 달빛네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agn0401/</t>
+          <t>https://open.kakao.com/o/sLs1Sagi</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5452,7 +5452,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5461,13 +5461,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5476,17 +5476,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>414262111</t>
+          <t>2052753261</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/414262111</t>
+          <t>https://m.place.naver.com/place/2052753261</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5498,29 +5498,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>그레이스네일</t>
+          <t>네일, 피어나</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>lumirode@naver.com</t>
+          <t>bbang52@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1379-5084</t>
+          <t>0507-1365-4941</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로248번길 24 갑룡프라자 2층</t>
+          <t>인천광역시 중구 하늘중앙로 193 314호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/grace_nail_?igsh=eGhhYXZlaGl0Z3hh&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/fe_ar_not/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5555,13 +5555,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>159</v>
+        <v>53</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5570,17 +5570,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1030374689</t>
+          <t>1581968497</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030374689</t>
+          <t>https://m.place.naver.com/place/1581968497</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5592,29 +5592,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>뉴얼리네일</t>
+          <t>블라썸뷰티 동성제약 풀리메디 영종점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kimaechin01@naver.com</t>
+          <t>yanstar80@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1429-1729</t>
+          <t>0507-1303-3553</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 선원면 중앙로 162-31 서희스타힐스 106동 1층 상가</t>
+          <t>인천광역시 중구 모랫말로 6-9 101호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nurely_nail</t>
+          <t>http://instagram.com/blossom_btl</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5649,13 +5649,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>25</v>
+        <v>408</v>
       </c>
       <c r="Q56" t="n">
-        <v>5</v>
+        <v>475</v>
       </c>
       <c r="R56" t="n">
-        <v>30</v>
+        <v>883</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5664,17 +5664,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2009541921</t>
+          <t>1867109358</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009541921</t>
+          <t>https://m.place.naver.com/place/1867109358</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5686,25 +5686,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>그리닷뷰티</t>
+          <t>네일 바이 담</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>dean0707@naver.com</t>
+          <t>11dldnjs@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>032-751-6686</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
+          <t>인천광역시 중구 햇내로13번길 17 프라임시티1차 102호 네일바이담</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nailby.dam</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5714,7 +5718,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5735,17 +5739,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>34</v>
+        <v>173</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5754,17 +5758,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1208135114</t>
+          <t>1880192448</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208135114</t>
+          <t>https://m.place.naver.com/place/1880192448</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5776,29 +5780,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>레푸스 강화점</t>
+          <t>템팅네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>refuss_ganghwa@naver.com</t>
+          <t>withkyra@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1409-2278</t>
+          <t>0507-1398-4155</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 충렬사로 25 남산빌딩 2층 202호</t>
+          <t>인천광역시 중구 햇내로안길 18-4 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@강화레푸스</t>
+          <t>https://www.instagram.com/tempting_nail</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5813,7 +5817,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5833,13 +5837,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>19</v>
+        <v>279</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R58" t="n">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5848,17 +5852,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1506333714</t>
+          <t>1951261120</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1506333714</t>
+          <t>https://m.place.naver.com/place/1951261120</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5879,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>juvide@naver.com</t>
+          <t>pooglemom@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -5927,13 +5931,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q59" t="n">
         <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5952,7 +5956,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5964,29 +5968,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>그릿네일</t>
+          <t>네일유희 하늘도시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>grit_nail@naver.com</t>
+          <t>kim960113@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1464-3789</t>
+          <t>0507-1492-3774</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디컬 2층 202호</t>
+          <t>인천광역시 중구 월촌길 28 102호 네일유희</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/grit.nail</t>
+          <t>https://www.instagram.com/nailyuhee</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6021,13 +6025,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="Q60" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="R60" t="n">
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6036,17 +6040,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1981189370</t>
+          <t>1310153514</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1981189370</t>
+          <t>https://m.place.naver.com/place/1310153514</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6058,29 +6062,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>아이온네일 인천영종점</t>
+          <t>그릿네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ym6030@naver.com</t>
+          <t>grit_nail@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1329-3883</t>
+          <t>0507-1464-3789</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로196번길 15-25 운서역반도유보라퍼스트지 상가동2층226호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디컬 2층 202호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ym6030</t>
+          <t>https://www.instagram.com/grit.nail</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6095,7 +6099,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6115,13 +6119,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>877</v>
+        <v>189</v>
       </c>
       <c r="Q61" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="R61" t="n">
-        <v>949</v>
+        <v>230</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6130,17 +6134,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1792903749</t>
+          <t>1981189370</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792903749</t>
+          <t>https://m.place.naver.com/place/1981189370</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6152,29 +6156,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>프프네일</t>
+          <t>엔샵</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>to_nail@naver.com</t>
+          <t>jiansritual@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1407-8841</t>
+          <t>0507-1404-6421</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 남문안길 5-1 1층</t>
+          <t>인천광역시 중구 하늘별빛로65번길 19 센타프라자 203호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ff__nail</t>
+          <t>https://blog.naver.com/jiansritual</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6189,7 +6193,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6209,13 +6213,13 @@
         </is>
       </c>
       <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
         <v>5</v>
       </c>
-      <c r="Q62" t="n">
-        <v>2</v>
-      </c>
       <c r="R62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6224,17 +6228,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1170338521</t>
+          <t>34362707</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1170338521</t>
+          <t>https://m.place.naver.com/place/34362707</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6246,34 +6250,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>더네일</t>
+          <t>뉴얼리네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>thenail_@naver.com</t>
+          <t>kimaechin01@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1481-0271</t>
+          <t>0507-1429-1729</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 20 215호</t>
+          <t>인천광역시 강화군 선원면 중앙로 162-31 서희스타힐스 106동 1층 상가</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Cf_KCSIrY34/?igshid=YmMyMTA2M2Y=</t>
+          <t>https://www.instagram.com/nurely_nail</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6283,7 +6287,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6303,13 +6307,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6318,17 +6322,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1979788121</t>
+          <t>2009541921</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979788121</t>
+          <t>https://m.place.naver.com/place/2009541921</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6340,34 +6344,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>옥스네일</t>
+          <t>슈가네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>odiyablog@naver.com</t>
+          <t>sugar_nail@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1434-0166</t>
+          <t>0507-1406-0391</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 139 777동(센텀베뉴 정문상가내) 103-2호</t>
+          <t>인천광역시 중구 흰바위로 36 영종주공스카이빌아파트 상가 103호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ok_s_nail</t>
+          <t>https://pf.kakao.com/_xlLxmyn</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6388,7 +6392,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6397,13 +6401,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="Q64" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6412,17 +6416,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2011391847</t>
+          <t>1533004146</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011391847</t>
+          <t>https://m.place.naver.com/place/1533004146</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6434,29 +6438,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>달빛네일</t>
+          <t>네일,윤</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>wltjsk12@naver.com</t>
+          <t>songyum84@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1316-8875</t>
+          <t>0507-1355-0330</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 310 2층 1호 달빛네일</t>
+          <t>인천광역시 중구 자연대로 37 2층 2호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sLs1Sagi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6466,7 +6470,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6482,22 +6486,22 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6506,17 +6510,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2052753261</t>
+          <t>2000502238</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2052753261</t>
+          <t>https://m.place.naver.com/place/2000502238</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6528,29 +6532,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>도도네일</t>
+          <t>퐁네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>dutjdgml70@naver.com</t>
+          <t>yegi1929@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1405-5840</t>
+          <t>0507-1340-7654</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 중구 두미포로 89 102호</t>
+          <t>인천광역시 중구 하늘달빛로 90-7 스카이에비뉴1 (6층)아띠스윤 내</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/dodonail.2024</t>
+          <t>http://www.instagram.com/_pongnail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6585,13 +6589,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>235</v>
+        <v>154</v>
       </c>
       <c r="Q66" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="R66" t="n">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6600,17 +6604,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>38321738</t>
+          <t>1591123938</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38321738</t>
+          <t>https://m.place.naver.com/place/1591123938</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6622,25 +6626,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ahashop nail</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>더 트윙클 네일</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>doll_a_wh@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1486-1185</t>
+          <t>0507-1488-2043</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 옹진군 북도면 장봉로238번길 66 1층</t>
+          <t>인천광역시 중구 흰바위로 262 럭키프라자 305호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/the.twinkle_nail1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6650,7 +6658,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6671,17 +6679,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6690,17 +6698,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1758864701</t>
+          <t>1809066919</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758864701</t>
+          <t>https://m.place.naver.com/place/1809066919</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6712,29 +6720,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>블랑디에 네일</t>
+          <t>프프네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>gkgmlwn2929@naver.com</t>
+          <t>to_nail@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1393-2128</t>
+          <t>0507-1407-8841</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 7-15 디에스지타워 10층 1003호</t>
+          <t>인천광역시 강화군 강화읍 남문안길 5-1 1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/blancdrenail</t>
+          <t>https://www.instagram.com/ff__nail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6760,7 +6768,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6769,13 +6777,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="Q68" t="n">
         <v>2</v>
       </c>
       <c r="R68" t="n">
-        <v>302</v>
+        <v>7</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6784,17 +6792,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1984068599</t>
+          <t>1170338521</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1984068599</t>
+          <t>https://m.place.naver.com/place/1170338521</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6806,29 +6814,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>오앤오네일</t>
+          <t>젤리쉬네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>bliss-mj@naver.com</t>
+          <t>thswltn011@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1319-2481</t>
+          <t>0507-1333-9838</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 88 7층 701호</t>
+          <t>인천광역시 중구 영종대로 166 솔리움센텀스카이 상가 1층 107호 젤리쉬네일</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ono__nail_studio</t>
+          <t>https://www.instagram.com/gelish._.nail_</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6863,13 +6871,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>91</v>
+        <v>1278</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="R69" t="n">
-        <v>92</v>
+        <v>1316</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6878,17 +6886,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2034560142</t>
+          <t>1825609603</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2034560142</t>
+          <t>https://m.place.naver.com/place/1825609603</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6900,29 +6908,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일은빛나</t>
+          <t>이뽐뷰티 강화점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>raronail@naver.com</t>
+          <t>leebbom_kh@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1375-7181</t>
+          <t>0507-1385-2307</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로196번길 15-25 반도유보라퍼스티지 상가동 1층 109호</t>
+          <t>인천광역시 강화군 강화읍 동문안길 7 B동 101호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_by_shine</t>
+          <t>https://blog.naver.com/leebbom_kh</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6937,7 +6945,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6957,13 +6965,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R70" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6972,17 +6980,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1399161803</t>
+          <t>1404657024</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399161803</t>
+          <t>https://m.place.naver.com/place/1404657024</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6994,29 +7002,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>이뽐뷰티 강화점</t>
+          <t>쟝스네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>leebbom_kh@naver.com</t>
+          <t>lee_jarang@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1385-2307</t>
+          <t>0507-1349-6922</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 동문안길 7 B동 101호</t>
+          <t>인천광역시 중구 하늘달빛로 80 504호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leebbom_kh</t>
+          <t>https://www.instagram.com/jangs_nail</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7031,7 +7039,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7051,13 +7059,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Q71" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R71" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7066,17 +7074,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1404657024</t>
+          <t>1748416887</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404657024</t>
+          <t>https://m.place.naver.com/place/1748416887</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7088,29 +7096,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>레푸스 인천영종점</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>lje9539@naver.com</t>
-        </is>
-      </c>
+          <t>ahashop nail</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1497-0007</t>
+          <t>0507-1486-1185</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로 100 신성하우스빌 3층 301호</t>
+          <t>인천광역시 옹진군 북도면 장봉로238번길 66 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_heyazi/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7120,7 +7124,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7141,17 +7145,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7160,17 +7164,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1131150431</t>
+          <t>1758864701</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131150431</t>
+          <t>https://m.place.naver.com/place/1758864701</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7182,34 +7186,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일 그대와</t>
+          <t>더리온</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>dodo1052@naver.com</t>
+          <t>jhjy101526@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1379-0491</t>
+          <t>032-836-4667</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 94 스타 타워1 507호</t>
+          <t>인천광역시 옹진군 백령면 백령로 282 더리온</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.withyou</t>
+          <t>http://pf.kakao.com/_rPaGn</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7230,22 +7234,22 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="Q73" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7254,17 +7258,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1267766371</t>
+          <t>1040252234</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267766371</t>
+          <t>https://m.place.naver.com/place/1040252234</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7276,29 +7280,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일이안</t>
+          <t>지니네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>wjstngusrn@naver.com</t>
+          <t>goto_seoul@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1467-1252</t>
+          <t>0507-1316-6480</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 47 610호</t>
+          <t>인천광역시 강화군 강화읍 남문안길32번길 8 2층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ian</t>
+          <t>http://www.instagram.com/jineenail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7333,13 +7337,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7348,17 +7352,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1117993147</t>
+          <t>1155579596</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117993147</t>
+          <t>https://m.place.naver.com/place/1155579596</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7370,29 +7374,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>쟝스네일</t>
+          <t>버디네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>lee_jarang@naver.com</t>
+          <t>hhj6910@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1349-6922</t>
+          <t>0507-1420-9856</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 80 504호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디칼 3층 309호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jangs_nail</t>
+          <t>https://www.instagram.com/buddy_nail__</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7427,13 +7431,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>105</v>
+        <v>620</v>
       </c>
       <c r="Q75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R75" t="n">
-        <v>111</v>
+        <v>622</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7442,17 +7446,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1748416887</t>
+          <t>1255393282</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748416887</t>
+          <t>https://m.place.naver.com/place/1255393282</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7464,29 +7468,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일917</t>
+          <t>무</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>mneilacademy@naver.com</t>
+          <t>sooks_room@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>032-751-0917</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 중구 화랑목로100번길 75 104호</t>
+          <t>인천광역시 강화군 강화읍 강화대로 394</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail.917</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7517,17 +7517,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>437</v>
+        <v>5</v>
       </c>
       <c r="Q76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>447</v>
+        <v>9</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7536,17 +7536,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1363080406</t>
+          <t>36721147</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363080406</t>
+          <t>https://m.place.naver.com/place/36721147</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/옹진군_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/옹진군_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>쏘니네일</t>
+          <t>네일917</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultramariine@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1485-3336</t>
+          <t>032-751-0917</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 284 110-1호</t>
+          <t>인천광역시 중구 화랑목로100번길 75 104호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssoninail</t>
+          <t>http://www.instagram.com/nail.917</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>12</v>
+        <v>439</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>13</v>
+        <v>449</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1226536825</t>
+          <t>1363080406</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226536825</t>
+          <t>https://m.place.naver.com/place/1363080406</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>도도네일</t>
+          <t>미뇽네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dutjdgml70@naver.com</t>
+          <t>akstjd1018@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1405-5840</t>
+          <t>0507-1381-9702</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 중구 두미포로 89 102호</t>
+          <t>인천광역시 강화군 강화읍 강화대로 347-1 101호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/dodonail.2024</t>
+          <t>http://pf.kakao.com/_hkxiqG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>238</v>
+        <v>125</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>244</v>
+        <v>128</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>38321738</t>
+          <t>1280952259</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38321738</t>
+          <t>https://m.place.naver.com/place/1280952259</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
+          <t>네일 그대와</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>vizarai@naver.com</t>
+          <t>dodo1052@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1327-8743</t>
+          <t>0507-1379-0491</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 14 301호 네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
+          <t>인천광역시 중구 하늘달빛로 94 스타 타워1 507호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vizarai</t>
+          <t>https://www.instagram.com/nail._.withyou</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>243</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>256</v>
+        <v>23</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1976884898</t>
+          <t>1267766371</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976884898</t>
+          <t>https://m.place.naver.com/place/1267766371</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>언니네일 페디베네 영종 운서점</t>
+          <t>네일위클로</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>botong56@naver.com</t>
+          <t>summerstar1984@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1416-6632</t>
+          <t>0507-1368-4179</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 중구 넙디로 47 백산빌딩 103호 언니네일 페디베네 영종 운서점</t>
+          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/botong56</t>
+          <t>https://www.instagram.com/nail.weclo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>205</v>
+        <v>76</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37101621</t>
+          <t>2038322752</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37101621</t>
+          <t>https://m.place.naver.com/place/2038322752</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일공간 영종하늘도시점</t>
+          <t>비너스네일앤뷰티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>juseul2@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1357-2207</t>
+          <t>0507-1309-4148</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 95 102동 108호</t>
+          <t>인천광역시 강화군 강화읍 신문길 42 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_gonggan1</t>
+          <t>https://www.instagram.com/venus_nail4148</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1000,10 +1000,10 @@
         <v>24</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2006802771</t>
+          <t>1141156599</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2006802771</t>
+          <t>https://m.place.naver.com/place/1141156599</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,25 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N.Nail</t>
+          <t>오앤오네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nailon22@naver.com</t>
+          <t>bliss-mj@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1319-2481</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 8 207호(운서동, 프라임시티3)</t>
+          <t>인천광역시 중구 하늘달빛로 88 7층 701호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.nail_3/</t>
+          <t>https://www.instagram.com/ono__nail_studio</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2001565256</t>
+          <t>2034560142</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001565256</t>
+          <t>https://m.place.naver.com/place/2034560142</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1128,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>라비쥬</t>
+          <t>네일오다</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sincity01@naver.com</t>
+          <t>jin568900@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1340-8384</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 15 세영프라자 4층</t>
+          <t>인천광역시 중구 자연대로 28 그랑블루인영종 209호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://instagram.com/salon_labijou</t>
+          <t>https://www.instagram.com/nail.oda</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>332</v>
+        <v>200</v>
       </c>
       <c r="Q8" t="n">
-        <v>403</v>
+        <v>43</v>
       </c>
       <c r="R8" t="n">
-        <v>735</v>
+        <v>243</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37064341</t>
+          <t>1153727265</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37064341</t>
+          <t>https://m.place.naver.com/place/1153727265</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>퍼플리네일</t>
+          <t>아이온네일 인천영종점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>u_un0709@naver.com</t>
+          <t>ym6030@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1315-4140</t>
+          <t>0507-1329-3883</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 선원면 중앙로 162-3 2층</t>
+          <t>인천광역시 중구 영종대로196번길 15-25 운서역반도유보라퍼스트지 상가동2층226호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/purply._.nail/</t>
+          <t>https://blog.naver.com/ym6030</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>41</v>
+        <v>885</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="R9" t="n">
-        <v>41</v>
+        <v>957</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2094549338</t>
+          <t>1792903749</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094549338</t>
+          <t>https://m.place.naver.com/place/1792903749</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>주드네일</t>
+          <t>네일이안</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>luv_gayeon0@naver.com</t>
+          <t>wjstngusrn@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1397-7996</t>
+          <t>0507-1467-1252</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 3 영종M타워 2층 201호 이철헤어커커 안</t>
+          <t>인천광역시 중구 자연대로 47 610호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/luv_gayeon0</t>
+          <t>https://www.instagram.com/nail_ian</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>459</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="R10" t="n">
-        <v>481</v>
+        <v>90</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1740443365</t>
+          <t>1117993147</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1740443365</t>
+          <t>https://m.place.naver.com/place/1117993147</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1406,20 +1406,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일,빛</t>
+          <t>아하뷰티샵</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ekeor0718@naver.com</t>
+          <t>ahasoft_crm@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1366-0805</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 193 조양타워 4층 409호</t>
+          <t>인천광역시 옹진군 북도면 장봉로238번길 66</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1459,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1646288604</t>
+          <t>1135765422</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1646288604</t>
+          <t>https://m.place.naver.com/place/1135765422</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>압구정네일샵</t>
+          <t>라비쥬</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bitna0614@naver.com</t>
+          <t>sincity01@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>032-751-0401</t>
+          <t>0507-1340-8384</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 중구 운남로 158 2층</t>
+          <t>인천광역시 중구 하늘중앙로195번길 15 세영프라자 4층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agn0401/</t>
+          <t>http://instagram.com/salon_labijou</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>18</v>
+        <v>332</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="R12" t="n">
-        <v>18</v>
+        <v>735</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>414262111</t>
+          <t>37064341</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/414262111</t>
+          <t>https://m.place.naver.com/place/37064341</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1594,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>레푸스 강화점</t>
+          <t>네일은영</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>refuss_ganghwa@naver.com</t>
+          <t>naileun_0@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1409-2278</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 충렬사로 25 남산빌딩 2층 202호</t>
+          <t>인천광역시 중구 흰바위로 45 118호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@강화레푸스</t>
+          <t>http://instagram.com/naileun_0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>19</v>
+        <v>375</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>19</v>
+        <v>381</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1506333714</t>
+          <t>1430851204</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1506333714</t>
+          <t>https://m.place.naver.com/place/1430851204</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1684,25 +1684,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일바이에스</t>
+          <t>옥스네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nufine@naver.com</t>
+          <t>odiyablog@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1434-0166</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로안길 14-5 102호 네일바이에스</t>
+          <t>인천광역시 중구 하늘달빛로 139 777동(센텀베뉴 정문상가내) 103-2호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailby_s</t>
+          <t>https://www.instagram.com/ok_s_nail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1737,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>337</v>
+        <v>135</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="R14" t="n">
-        <v>340</v>
+        <v>169</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,17 +1756,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1163668428</t>
+          <t>2011391847</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163668428</t>
+          <t>https://m.place.naver.com/place/2011391847</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1774,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>태봉씨뷰티살롱&amp;LCN공식 인증매장</t>
+          <t>네일,윤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xogns07@naver.com</t>
+          <t>songyum84@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1330-1831</t>
+          <t>0507-1355-0330</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 20 9층 910호</t>
+          <t>인천광역시 중구 자연대로 37 2층 2호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xogns07</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1806,12 +1810,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1827,17 +1831,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>455</v>
+        <v>19</v>
       </c>
       <c r="Q15" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>568</v>
+        <v>19</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1381683377</t>
+          <t>2000502238</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381683377</t>
+          <t>https://m.place.naver.com/place/2000502238</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1868,29 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일핫플</t>
+          <t>루시네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dydals1wj@naver.com</t>
+          <t>dkfma2329@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>032-747-0321</t>
+          <t>0507-1321-0922</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 38 208호 네일핫플</t>
+          <t>인천광역시 중구 자연대로 40 비젼프라자2 509호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hotple?igsh=MTl4dmd6ZGdlcHF4dA==</t>
+          <t>https://www.instagram.com/lllucynail_</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1916,7 +1920,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1925,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>180</v>
+        <v>3</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1813910551</t>
+          <t>691165364</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1813910551</t>
+          <t>https://m.place.naver.com/place/691165364</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1962,29 +1966,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일파르크</t>
+          <t>쟝스네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>liphop2588@naver.com</t>
+          <t>lee_jarang@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1385-0712</t>
+          <t>0507-1349-6922</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 중구 화랑목로 50-7 102호</t>
+          <t>인천광역시 중구 하늘달빛로 80 504호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_parc</t>
+          <t>https://www.instagram.com/jangs_nail</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2019,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1965314720</t>
+          <t>1748416887</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965314720</t>
+          <t>https://m.place.naver.com/place/1748416887</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2056,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일바유</t>
+          <t>네일, 피어나</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fhwmay@naver.com</t>
+          <t>bbang52@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1414-0777</t>
+          <t>0507-1365-4941</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 258 센타프라자 2층 208호</t>
+          <t>인천광역시 중구 하늘중앙로 193 314호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.bayu</t>
+          <t>https://www.instagram.com/fe_ar_not/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2113,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>288</v>
+        <v>54</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>293</v>
+        <v>55</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1489158637</t>
+          <t>1581968497</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1489158637</t>
+          <t>https://m.place.naver.com/place/1581968497</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2154,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>더예쁨네일피부</t>
+          <t>그리닷뷰티</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>tlsrl0104@naver.com</t>
+          <t>dean0707@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2163,17 +2167,17 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 37 스카이가든 2층 206호</t>
+          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.theyepm.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2199,17 +2203,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2218,17 +2222,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2044624904</t>
+          <t>1208135114</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044624904</t>
+          <t>https://m.place.naver.com/place/1208135114</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2240,29 +2244,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>옥스네일</t>
+          <t>그릿네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>odiyablog@naver.com</t>
+          <t>grit_nail@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1434-0166</t>
+          <t>0507-1464-3789</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 139 777동(센텀베뉴 정문상가내) 103-2호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디컬 2층 202호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ok_s_nail</t>
+          <t>https://www.instagram.com/grit.nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2297,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="Q20" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,17 +2316,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2011391847</t>
+          <t>1981189370</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011391847</t>
+          <t>https://m.place.naver.com/place/1981189370</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2334,29 +2338,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아하뷰티샵</t>
+          <t>레푸스 강화점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ahasoft_crm@naver.com</t>
+          <t>refuss_ganghwa@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1366-0805</t>
+          <t>0507-1409-2278</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 옹진군 북도면 장봉로238번길 66</t>
+          <t>인천광역시 강화군 강화읍 충렬사로 25 남산빌딩 2층 202호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.youtube.com/@강화레푸스</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2366,12 +2370,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2387,17 +2391,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,17 +2410,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1135765422</t>
+          <t>1506333714</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135765422</t>
+          <t>https://m.place.naver.com/place/1506333714</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2428,29 +2432,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일917</t>
+          <t>태봉씨뷰티살롱&amp;LCN공식 인증매장</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>xogns07@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>032-751-0917</t>
+          <t>0507-1330-1831</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 중구 화랑목로100번길 75 104호</t>
+          <t>인천광역시 중구 하늘중앙로225번길 20 9층 910호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail.917</t>
+          <t>https://blog.naver.com/xogns07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2465,7 +2469,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2485,13 +2489,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="R22" t="n">
-        <v>448</v>
+        <v>568</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,17 +2504,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1363080406</t>
+          <t>1381683377</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363080406</t>
+          <t>https://m.place.naver.com/place/1381683377</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2522,34 +2526,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일이안</t>
+          <t>슈가네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>wjstngusrn@naver.com</t>
+          <t>junge1004j@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1467-1252</t>
+          <t>0507-1406-0391</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 47 610호</t>
+          <t>인천광역시 중구 흰바위로 36 영종주공스카이빌아파트 상가 103호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ian</t>
+          <t>https://pf.kakao.com/_xlLxmyn</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2570,7 +2574,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2579,13 +2583,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c r="Q23" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2594,17 +2598,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1117993147</t>
+          <t>1533004146</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117993147</t>
+          <t>https://m.place.naver.com/place/1533004146</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2616,29 +2620,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일 그대와</t>
+          <t>그때 그 네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dodo1052@naver.com</t>
+          <t>goodbyealice@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1379-0491</t>
+          <t>0507-1301-9627</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 94 스타 타워1 507호</t>
+          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.withyou</t>
+          <t>https://www.instagram.com/_ggnail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2673,13 +2677,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,17 +2692,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1267766371</t>
+          <t>1380919881</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267766371</t>
+          <t>https://m.place.naver.com/place/1380919881</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2710,29 +2714,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>플레이버네일</t>
+          <t>달빛네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>oao08@naver.com</t>
+          <t>duoshan_sz@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1382-0428</t>
+          <t>0507-1316-8875</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 중구 운서로7번길 60 1층 103호</t>
+          <t>인천광역시 강화군 강화읍 강화대로 310 201호 달빛네일</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flavornail?igsh=MWgwY3luaWppNHdtZg%3D%3D&amp;utm_source=qr</t>
+          <t>https://open.kakao.com/o/sLs1Sagi</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2758,7 +2762,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2767,13 +2771,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>255</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>258</v>
+        <v>2</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2786,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1693860525</t>
+          <t>2052753261</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693860525</t>
+          <t>https://m.place.naver.com/place/2052753261</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2804,29 +2808,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>바비수네일&amp;태닝</t>
+          <t>네일바이에스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>vavisu_nail@naver.com</t>
+          <t>nufine@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>032-752-8700</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 94 스타타워 407호</t>
+          <t>인천광역시 중구 햇내로안길 14-5 102호 네일바이에스</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vavisu_nail</t>
+          <t>https://www.instagram.com/nailby_s</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3</v>
       </c>
-      <c r="Q26" t="n">
-        <v>10</v>
-      </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>343</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2876,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>35516411</t>
+          <t>1163668428</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35516411</t>
+          <t>https://m.place.naver.com/place/1163668428</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2898,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>오앤오네일</t>
+          <t>네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>bliss-mj@naver.com</t>
+          <t>vizarai@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1319-2481</t>
+          <t>0507-1327-8743</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 88 7층 701호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 14 301호 네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ono__nail_studio</t>
+          <t>https://blog.naver.com/vizarai</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>93</v>
+        <v>243</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +2970,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2034560142</t>
+          <t>1976884898</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2034560142</t>
+          <t>https://m.place.naver.com/place/1976884898</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2992,34 +2992,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일했냥</t>
+          <t>원네일앤뷰티 영종하늘도시점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mementomori-24@naver.com</t>
+          <t>wonnail0929@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0507-1346-6543</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 90-27 109호</t>
+          <t>인천광역시 중구 하늘달빛로 70 메디피아빌딩 304호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_PxiixmG</t>
+          <t>https://blog.naver.com/wonnail0929</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3029,7 +3025,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3040,7 +3036,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3049,13 +3045,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1515</v>
+        <v>196</v>
       </c>
       <c r="Q28" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="R28" t="n">
-        <v>1581</v>
+        <v>214</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3060,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1874909116</t>
+          <t>1259164731</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874909116</t>
+          <t>https://m.place.naver.com/place/1259164731</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3086,29 +3082,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아이온네일 인천영종점</t>
+          <t>템팅네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ym6030@naver.com</t>
+          <t>withkyra@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1329-3883</t>
+          <t>0507-1398-4155</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로196번길 15-25 운서역반도유보라퍼스트지 상가동2층226호</t>
+          <t>인천광역시 중구 햇내로안길 18-4 1층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ym6030</t>
+          <t>https://www.instagram.com/tempting_nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3123,7 +3119,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3143,13 +3139,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>883</v>
+        <v>280</v>
       </c>
       <c r="Q29" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
-        <v>955</v>
+        <v>286</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3158,17 +3154,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1792903749</t>
+          <t>1951261120</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792903749</t>
+          <t>https://m.place.naver.com/place/1951261120</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3180,29 +3176,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>스튜디오공감</t>
+          <t>주드네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>studi5gonggam_art@naver.com</t>
+          <t>luv_gayeon0@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1380-0311</t>
+          <t>0507-1397-7996</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호 스튜디오공감</t>
+          <t>인천광역시 중구 하늘달빛로 82 4층 405호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/studi5gonggam_art</t>
+          <t>https://blog.naver.com/luv_gayeon0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3237,13 +3233,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>206</v>
+        <v>460</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
-        <v>219</v>
+        <v>482</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3252,17 +3248,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1085588496</t>
+          <t>1740443365</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1085588496</t>
+          <t>https://m.place.naver.com/place/1740443365</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3274,29 +3270,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일더스킨</t>
+          <t>오늘네일샵</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feel3051@naver.com</t>
+          <t>webmaia21@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1411-0441</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 258 211호</t>
+          <t>충청남도 서산시 대산읍 충의로 1889</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/_nail_2day</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3306,7 +3298,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3327,17 +3319,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3346,17 +3338,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1314782883</t>
+          <t>1283160281</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314782883</t>
+          <t>https://m.place.naver.com/place/1283160281</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3368,29 +3360,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>소소네일</t>
+          <t>언니네일 페디베네 영종 운서점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>iamkimz@naver.com</t>
+          <t>botong56@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1327-9628</t>
+          <t>0507-1416-6632</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로404번길 9 2층 윈썸헤어&amp;소소네일</t>
+          <t>인천광역시 중구 넙디로 47 백산빌딩 103호 언니네일 페디베네 영종 운서점</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sosonail_y?igsh=djM3NzVmbHM5eDRo&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/botong56</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3405,7 +3397,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3425,13 +3417,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>205</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,17 +3432,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1958174820</t>
+          <t>37101621</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958174820</t>
+          <t>https://m.place.naver.com/place/37101621</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3462,29 +3454,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>두손네일</t>
+          <t>블랑디에 네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>doosonnail@naver.com</t>
+          <t>gkgmlwn2929@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1401-4970</t>
+          <t>0507-1393-2128</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 31 에어로시티</t>
+          <t>인천광역시 중구 하늘별빛로65번길 7-15 디에스지타워 10층 1003호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jangjeongsnyi/</t>
+          <t>https://www.instagram.com/blancdrenail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3510,7 +3502,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3519,13 +3511,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>302</v>
       </c>
       <c r="Q33" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>68</v>
+        <v>304</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,17 +3526,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>125000879</t>
+          <t>1984068599</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/125000879</t>
+          <t>https://m.place.naver.com/place/1984068599</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3556,25 +3548,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>가디스뷰티샵</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>goddess503@naver.com</t>
-        </is>
-      </c>
+          <t>ahashop nail</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1486-1185</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 7-9 스카이타워5층 503호</t>
+          <t>인천광역시 옹진군 북도면 장봉로238번길 66 1층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goddess503</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3584,12 +3576,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3605,17 +3597,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3624,17 +3616,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1848560502</t>
+          <t>1758864701</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1848560502</t>
+          <t>https://m.place.naver.com/place/1758864701</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3646,29 +3638,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>오니네일</t>
+          <t>소소네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>wjsska1907@naver.com</t>
+          <t>iamkimz@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1311-0663</t>
+          <t>0507-1327-9628</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 갑룡길 29 1층, 카페88 내부위치</t>
+          <t>인천광역시 강화군 강화읍 강화대로404번길 9 2층 윈썸헤어&amp;소소네일</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://instagram.com/oninail_</t>
+          <t>https://www.instagram.com/sosonail_y?igsh=djM3NzVmbHM5eDRo&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3703,13 +3695,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3718,17 +3710,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1245994155</t>
+          <t>1958174820</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245994155</t>
+          <t>https://m.place.naver.com/place/1958174820</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3740,29 +3732,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>레푸스 인천영종점</t>
+          <t>네일은빛나</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>lje9539@naver.com</t>
+          <t>raronail@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1497-0007</t>
+          <t>0507-1375-7181</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로 100 신성하우스빌 3층 301호</t>
+          <t>인천광역시 중구 영종대로196번길 15-25 반도유보라퍼스티지 상가동 1층 109호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_heyazi/</t>
+          <t>https://www.instagram.com/nail_by_shine</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3797,13 +3789,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="Q36" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>222</v>
+        <v>127</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3812,17 +3804,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1131150431</t>
+          <t>1399161803</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131150431</t>
+          <t>https://m.place.naver.com/place/1399161803</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3834,25 +3826,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>오늘네일샵</t>
+          <t>도도네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>webmaia21@naver.com</t>
+          <t>mh95577@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1405-5840</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>충청남도 서산시 대산읍 충의로 1889</t>
+          <t>인천광역시 중구 두미포로 89 102호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://instagram.com/_nail_2day</t>
+          <t>http://www.instagram.com/dodonail.2024</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3887,13 +3883,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>239</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>245</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,17 +3898,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1283160281</t>
+          <t>38321738</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283160281</t>
+          <t>https://m.place.naver.com/place/38321738</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3924,29 +3920,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>그레이스네일</t>
+          <t>두손네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>lumirode@naver.com</t>
+          <t>doosonnail@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1379-5084</t>
+          <t>0507-1401-4970</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로248번길 24 갑룡프라자 2층</t>
+          <t>인천광역시 중구 흰바위로 31 에어로시티</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/grace_nail_?igsh=eGhhYXZlaGl0Z3hh&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/jangjeongsnyi/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3981,13 +3977,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="R38" t="n">
-        <v>160</v>
+        <v>68</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,17 +3992,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1030374689</t>
+          <t>125000879</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030374689</t>
+          <t>https://m.place.naver.com/place/125000879</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4018,30 +4014,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>라르떼네일</t>
+          <t>네일 두나</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>limkyungmi10@naver.com</t>
+          <t>pooglemom@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1314-5785</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 11 해솔프라자 403-1호</t>
+          <t>인천광역시 중구 두미포로 60 101호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rarete_nail02</t>
+          <t>https://pf.kakao.com/_XVSxbn</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4062,7 +4062,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4071,13 +4071,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,17 +4086,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1844112944</t>
+          <t>1880658481</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1844112944</t>
+          <t>https://m.place.naver.com/place/1880658481</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4108,34 +4108,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>미뇽네일</t>
+          <t>더 트윙클 네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>akstjd1018@naver.com</t>
+          <t>doll_a_wh@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1381-9702</t>
+          <t>0507-1488-2043</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 347-1 101호</t>
+          <t>인천광역시 중구 흰바위로 262 럭키프라자 305호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hkxiqG</t>
+          <t>https://www.instagram.com/the.twinkle_nail1</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4156,7 +4156,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4165,13 +4165,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>125</v>
+        <v>414</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R40" t="n">
-        <v>128</v>
+        <v>420</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,17 +4180,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1280952259</t>
+          <t>1809066919</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280952259</t>
+          <t>https://m.place.naver.com/place/1809066919</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4202,25 +4202,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>제이네일</t>
+          <t>블라썸뷰티 동성제약 풀리메디 영종점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>rhkdmswl@naver.com</t>
+          <t>yanstar80@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1303-3553</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 향나무길28번길 13-1</t>
+          <t>인천광역시 중구 모랫말로 6-9 101호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j.nail_shop</t>
+          <t>http://instagram.com/blossom_btl</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4255,13 +4259,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5</v>
+        <v>409</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>475</v>
       </c>
       <c r="R41" t="n">
-        <v>7</v>
+        <v>884</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4270,17 +4274,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1237271418</t>
+          <t>1867109358</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237271418</t>
+          <t>https://m.place.naver.com/place/1867109358</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4292,25 +4296,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일오다</t>
+          <t>네일유희 하늘도시</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jin568900@naver.com</t>
+          <t>kim960113@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1492-3774</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 28 그랑블루인영종 209호</t>
+          <t>인천광역시 중구 월촌길 28 102호 네일유희</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.oda</t>
+          <t>https://www.instagram.com/nailyuhee</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4345,13 +4353,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="Q42" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="R42" t="n">
-        <v>242</v>
+        <v>88</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4360,17 +4368,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1153727265</t>
+          <t>1310153514</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153727265</t>
+          <t>https://m.place.naver.com/place/1310153514</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4382,29 +4390,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>루시네일</t>
+          <t>네일파르크</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>hyeoniizzang@naver.com</t>
+          <t>liphop2588@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1321-0922</t>
+          <t>0507-1385-0712</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 40 비젼프라자2 509호</t>
+          <t>인천광역시 중구 화랑목로 50-7 102호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lllucynail_</t>
+          <t>http://www.instagram.com/nail_parc</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4439,13 +4447,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="R43" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4454,17 +4462,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>691165364</t>
+          <t>1965314720</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/691165364</t>
+          <t>https://m.place.naver.com/place/1965314720</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4476,25 +4484,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일은영</t>
+          <t>프프네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>naileun_0@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1407-8841</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 45 118호</t>
+          <t>인천광역시 강화군 강화읍 남문안길 5-1 1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://instagram.com/naileun_0</t>
+          <t>https://www.instagram.com/ff__nail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4529,13 +4541,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>376</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>382</v>
+        <v>7</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4544,17 +4556,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1430851204</t>
+          <t>1170338521</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430851204</t>
+          <t>https://m.place.naver.com/place/1170338521</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4566,25 +4578,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>그리닷뷰티</t>
+          <t>오니네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dean0707@naver.com</t>
+          <t>wjsska1907@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1311-0663</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
+          <t>인천광역시 강화군 강화읍 갑룡길 29 1층, 카페88 내부위치</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/oninail_</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4594,7 +4610,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4615,17 +4631,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R45" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4634,17 +4650,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1208135114</t>
+          <t>1245994155</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208135114</t>
+          <t>https://m.place.naver.com/place/1245994155</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4656,29 +4672,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일위클로</t>
+          <t>바비수네일&amp;태닝</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>summerstar1984@naver.com</t>
+          <t>vavisu_nail@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1368-4179</t>
+          <t>032-752-8700</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
+          <t>인천광역시 중구 하늘달빛로 94 스타타워 407호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.weclo</t>
+          <t>https://blog.naver.com/vavisu_nail</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4693,7 +4709,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4709,17 +4725,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R46" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4728,17 +4744,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2038322752</t>
+          <t>35516411</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038322752</t>
+          <t>https://m.place.naver.com/place/35516411</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4750,29 +4766,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일은빛나</t>
+          <t>네일바유</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>raronail@naver.com</t>
+          <t>fhwmay@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1375-7181</t>
+          <t>0507-1414-0777</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로196번길 15-25 반도유보라퍼스티지 상가동 1층 109호</t>
+          <t>인천광역시 중구 흰바위로 258 센타프라자 2층 208호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_by_shine</t>
+          <t>https://www.instagram.com/nail._.bayu</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4807,13 +4823,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>122</v>
+        <v>288</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>126</v>
+        <v>293</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4822,17 +4838,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1399161803</t>
+          <t>1489158637</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399161803</t>
+          <t>https://m.place.naver.com/place/1489158637</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4844,29 +4860,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>루비네일</t>
+          <t>스튜디오공감</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ruby1004_mj@naver.com</t>
+          <t>studi5gonggam_art@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1342-4252</t>
+          <t>0507-1380-0311</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 중앙로 68 하나로마트 2층 214호</t>
+          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호 스튜디오공감</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/studi5gonggam_art</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4876,12 +4892,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4897,17 +4913,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R48" t="n">
-        <v>14</v>
+        <v>219</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4916,17 +4932,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1791159276</t>
+          <t>1085588496</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1791159276</t>
+          <t>https://m.place.naver.com/place/1085588496</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4938,25 +4954,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>원네일앤뷰티 영종하늘도시점</t>
+          <t>레푸스 인천영종점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>wonnail0929@naver.com</t>
+          <t>lje9539@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1497-0007</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 70 메디피아빌딩 304호</t>
+          <t>인천광역시 중구 영종대로 100 신성하우스빌 3층 301호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wonnail0929</t>
+          <t>https://www.instagram.com/nail_heyazi/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4971,7 +4991,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4991,13 +5011,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="R49" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5006,17 +5026,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1259164731</t>
+          <t>1131150431</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259164731</t>
+          <t>https://m.place.naver.com/place/1131150431</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5028,29 +5048,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일 또 보니</t>
+          <t>플레이버네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>to_nail@naver.com</t>
+          <t>oao08@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1355-4749</t>
+          <t>0507-1382-0428</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 18 효정타워 305호</t>
+          <t>인천광역시 중구 운서로7번길 60 1층 103호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ddoboni</t>
+          <t>https://www.instagram.com/flavornail?igsh=MWgwY3luaWppNHdtZg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5085,13 +5105,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>327</v>
+        <v>257</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R50" t="n">
-        <v>337</v>
+        <v>260</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5100,17 +5120,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1350394025</t>
+          <t>1693860525</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350394025</t>
+          <t>https://m.place.naver.com/place/1693860525</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5122,29 +5142,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>그때 그 네일</t>
+          <t>더리온</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>goodbyealice@naver.com</t>
+          <t>jhjy101526@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1301-9627</t>
+          <t>032-836-4667</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호</t>
+          <t>인천광역시 옹진군 백령면 백령로 282 더리온</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ggnail</t>
+          <t>http://pf.kakao.com/_rPaGn</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5159,7 +5179,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5170,22 +5190,22 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>133</v>
+        <v>40</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5194,17 +5214,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1380919881</t>
+          <t>1040252234</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1380919881</t>
+          <t>https://m.place.naver.com/place/1040252234</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5216,29 +5236,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>블랑디에 네일</t>
+          <t>N.Nail</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>gkgmlwn2929@naver.com</t>
+          <t>nailon22@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0507-1393-2128</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 7-15 디에스지타워 10층 1003호</t>
+          <t>인천광역시 중구 햇내로13번길 8 207호(운서동, 프라임시티3)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/blancdrenail</t>
+          <t>https://www.instagram.com/n.nail_3/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5264,7 +5280,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5273,13 +5289,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>300</v>
+        <v>9</v>
       </c>
       <c r="Q52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>302</v>
+        <v>10</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5288,17 +5304,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1984068599</t>
+          <t>2001565256</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1984068599</t>
+          <t>https://m.place.naver.com/place/2001565256</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5310,44 +5326,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>더네일</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>thenail_@naver.com</t>
-        </is>
-      </c>
+          <t>루비네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1481-0271</t>
+          <t>0507-1342-4252</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 20 215호</t>
+          <t>인천광역시 강화군 강화읍 중앙로 68 하나로마트 2층 214호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Cf_KCSIrY34/?igshid=YmMyMTA2M2Y=</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5363,17 +5375,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5382,17 +5394,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1979788121</t>
+          <t>1791159276</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979788121</t>
+          <t>https://m.place.naver.com/place/1791159276</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5404,29 +5416,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>달빛네일</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>duoshan_sz@naver.com</t>
-        </is>
-      </c>
+          <t>퐁네일</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1316-8875</t>
+          <t>0507-1340-7654</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 310 201호 달빛네일</t>
+          <t>인천광역시 중구 하늘달빛로 90-7 스카이에비뉴1 (6층)아띠스윤 내</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sLs1Sagi</t>
+          <t>http://www.instagram.com/_pongnail</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5452,7 +5460,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5461,13 +5469,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5476,17 +5484,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2052753261</t>
+          <t>1591123938</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2052753261</t>
+          <t>https://m.place.naver.com/place/1591123938</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5498,29 +5506,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일, 피어나</t>
+          <t>쏘니네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bbang52@naver.com</t>
+          <t>ultramariine@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1365-4941</t>
+          <t>0507-1485-3336</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 193 314호</t>
+          <t>인천광역시 중구 흰바위로 284 110-1호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fe_ar_not/</t>
+          <t>https://www.instagram.com/ssoninail</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5555,13 +5563,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5570,17 +5578,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1581968497</t>
+          <t>1226536825</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581968497</t>
+          <t>https://m.place.naver.com/place/1226536825</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5592,29 +5600,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>블라썸뷰티 동성제약 풀리메디 영종점</t>
+          <t>네일더스킨</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>yanstar80@naver.com</t>
+          <t>feel3051@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1303-3553</t>
+          <t>0507-1411-0441</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 중구 모랫말로 6-9 101호</t>
+          <t>인천광역시 중구 흰바위로 258 211호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://instagram.com/blossom_btl</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5624,7 +5632,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5645,17 +5653,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>883</v>
+        <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5664,17 +5672,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1867109358</t>
+          <t>1314782883</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867109358</t>
+          <t>https://m.place.naver.com/place/1314782883</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5686,39 +5694,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일 바이 담</t>
+          <t>더예쁨네일피부</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>11dldnjs@naver.com</t>
+          <t>tlsrl0104@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>032-751-6686</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 17 프라임시티1차 102호 네일바이담</t>
+          <t>인천광역시 중구 자연대로 37 스카이가든 2층 206호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailby.dam</t>
+          <t>https://www.theyepm.com</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5743,13 +5747,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5758,17 +5762,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1880192448</t>
+          <t>2044624904</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880192448</t>
+          <t>https://m.place.naver.com/place/2044624904</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5780,29 +5784,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>템팅네일</t>
+          <t>가디스뷰티샵</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>withkyra@naver.com</t>
+          <t>goddess503@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0507-1398-4155</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로안길 18-4 1층</t>
+          <t>인천광역시 중구 하늘별빛로65번길 7-9 스카이타워5층 503호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tempting_nail</t>
+          <t>https://blog.naver.com/goddess503</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5837,13 +5837,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>279</v>
+        <v>45</v>
       </c>
       <c r="Q58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>285</v>
+        <v>50</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5852,17 +5852,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1951261120</t>
+          <t>1848560502</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1951261120</t>
+          <t>https://m.place.naver.com/place/1848560502</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5874,34 +5874,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일 두나</t>
+          <t>압구정네일샵</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>pooglemom@naver.com</t>
+          <t>bitna0614@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1314-5785</t>
+          <t>032-751-0401</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 중구 두미포로 60 101호</t>
+          <t>인천광역시 중구 운남로 158 2층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_XVSxbn</t>
+          <t>https://www.instagram.com/agn0401/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5922,7 +5922,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5931,13 +5931,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5946,17 +5946,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1880658481</t>
+          <t>414262111</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880658481</t>
+          <t>https://m.place.naver.com/place/414262111</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5968,29 +5968,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일유희 하늘도시</t>
+          <t>지니네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kim960113@naver.com</t>
+          <t>goto_seoul@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1492-3774</t>
+          <t>0507-1316-6480</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 중구 월촌길 28 102호 네일유희</t>
+          <t>인천광역시 강화군 강화읍 남문안길32번길 8 2층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailyuhee</t>
+          <t>http://www.instagram.com/jineenail</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6040,17 +6040,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1310153514</t>
+          <t>1155579596</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310153514</t>
+          <t>https://m.place.naver.com/place/1155579596</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6062,29 +6062,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>그릿네일</t>
+          <t>이뽐뷰티 강화점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>grit_nail@naver.com</t>
+          <t>leebbom_kh@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1464-3789</t>
+          <t>0507-1385-2307</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디컬 2층 202호</t>
+          <t>인천광역시 강화군 강화읍 동문안길 7 B동 101호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/grit.nail</t>
+          <t>https://blog.naver.com/leebbom_kh</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6119,13 +6119,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="Q61" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="R61" t="n">
-        <v>230</v>
+        <v>115</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6134,17 +6134,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1981189370</t>
+          <t>1404657024</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1981189370</t>
+          <t>https://m.place.naver.com/place/1404657024</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6156,29 +6156,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>엔샵</t>
+          <t>버디네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jiansritual@naver.com</t>
+          <t>hhj6910@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1404-6421</t>
+          <t>0507-1420-9856</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 19 센타프라자 203호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디칼 3층 309호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jiansritual</t>
+          <t>https://www.instagram.com/buddy_nail__</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6213,13 +6213,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>5</v>
+        <v>623</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6228,17 +6228,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>34362707</t>
+          <t>1255393282</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34362707</t>
+          <t>https://m.place.naver.com/place/1255393282</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6250,29 +6250,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>뉴얼리네일</t>
+          <t>네일핫플</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kimaechin01@naver.com</t>
+          <t>dydals1wj@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1429-1729</t>
+          <t>032-747-0321</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 선원면 중앙로 162-31 서희스타힐스 106동 1층 상가</t>
+          <t>인천광역시 중구 자연대로 38 208호 네일핫플</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nurely_nail</t>
+          <t>https://www.instagram.com/nail_hotple?igsh=MTl4dmd6ZGdlcHF4dA==</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6298,7 +6298,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>26</v>
+        <v>175</v>
       </c>
       <c r="Q63" t="n">
         <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6322,17 +6322,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2009541921</t>
+          <t>1813910551</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009541921</t>
+          <t>https://m.place.naver.com/place/1813910551</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6344,34 +6344,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>슈가네일</t>
+          <t>뉴얼리네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sugar_nail@naver.com</t>
+          <t>kimaechin01@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1406-0391</t>
+          <t>0507-1429-1729</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 36 영종주공스카이빌아파트 상가 103호</t>
+          <t>인천광역시 강화군 선원면 중앙로 162-31 서희스타힐스 106동 1층 상가</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xlLxmyn</t>
+          <t>https://www.instagram.com/nurely_nail</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6392,7 +6392,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6401,13 +6401,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>169</v>
+        <v>27</v>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R64" t="n">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6416,17 +6416,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1533004146</t>
+          <t>2009541921</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533004146</t>
+          <t>https://m.place.naver.com/place/2009541921</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6438,29 +6438,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일,윤</t>
+          <t>네일 또 보니</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>songyum84@naver.com</t>
+          <t>yellowground_@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1355-0330</t>
+          <t>0507-1355-4749</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 37 2층 2호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 18 효정타워 305호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_ddoboni</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>15</v>
+        <v>328</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R65" t="n">
-        <v>15</v>
+        <v>338</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6510,17 +6510,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2000502238</t>
+          <t>1350394025</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000502238</t>
+          <t>https://m.place.naver.com/place/1350394025</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6532,29 +6532,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>퐁네일</t>
+          <t>그레이스네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>yegi1929@naver.com</t>
+          <t>lumirode@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1340-7654</t>
+          <t>0507-1379-5084</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 90-7 스카이에비뉴1 (6층)아띠스윤 내</t>
+          <t>인천광역시 강화군 강화읍 강화대로248번길 24 갑룡프라자 2층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_pongnail</t>
+          <t>https://www.instagram.com/grace_nail_?igsh=eGhhYXZlaGl0Z3hh&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6589,13 +6589,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="Q66" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6604,17 +6604,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1591123938</t>
+          <t>1030374689</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591123938</t>
+          <t>https://m.place.naver.com/place/1030374689</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6626,29 +6626,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>더 트윙클 네일</t>
+          <t>엔샵</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>doll_a_wh@naver.com</t>
+          <t>jiansritual@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1488-2043</t>
+          <t>0507-1404-6421</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 262 럭키프라자 305호</t>
+          <t>인천광역시 중구 하늘별빛로65번길 19 센타프라자 203호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the.twinkle_nail1</t>
+          <t>https://blog.naver.com/jiansritual</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R67" t="n">
-        <v>420</v>
+        <v>5</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6698,17 +6698,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1809066919</t>
+          <t>34362707</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1809066919</t>
+          <t>https://m.place.naver.com/place/34362707</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6720,34 +6720,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>프프네일</t>
+          <t>네일했냥</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>to_nail@naver.com</t>
+          <t>mementomori-24@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1407-8841</t>
+          <t>0507-1346-6543</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 남문안길 5-1 1층</t>
+          <t>인천광역시 중구 하늘달빛로 90-27 109호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ff__nail</t>
+          <t>http://pf.kakao.com/_PxiixmG</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6768,7 +6768,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6777,13 +6777,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>5</v>
+        <v>1518</v>
       </c>
       <c r="Q68" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="R68" t="n">
-        <v>7</v>
+        <v>1584</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1170338521</t>
+          <t>1874909116</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1170338521</t>
+          <t>https://m.place.naver.com/place/1874909116</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6814,29 +6814,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>젤리쉬네일</t>
+          <t>네일,빛</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>thswltn011@naver.com</t>
+          <t>ekeor0718@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0507-1333-9838</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로 166 솔리움센텀스카이 상가 1층 107호 젤리쉬네일</t>
+          <t>인천광역시 중구 하늘중앙로 193 조양타워 4층 409호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gelish._.nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6846,7 +6842,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6867,17 +6863,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1278</v>
+        <v>104</v>
       </c>
       <c r="Q69" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="R69" t="n">
-        <v>1316</v>
+        <v>109</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6886,17 +6882,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1825609603</t>
+          <t>1646288604</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1825609603</t>
+          <t>https://m.place.naver.com/place/1646288604</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6908,29 +6904,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>이뽐뷰티 강화점</t>
+          <t>퍼플리네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>leebbom_kh@naver.com</t>
+          <t>u_un0709@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1385-2307</t>
+          <t>0507-1315-4140</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 동문안길 7 B동 101호</t>
+          <t>인천광역시 강화군 선원면 중앙로 162-3 2층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leebbom_kh</t>
+          <t>https://www.instagram.com/purply._.nail/</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6945,7 +6941,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6965,13 +6961,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="Q70" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6980,17 +6976,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1404657024</t>
+          <t>2094549338</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404657024</t>
+          <t>https://m.place.naver.com/place/2094549338</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7002,29 +6998,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>쟝스네일</t>
+          <t>젤리쉬네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>lee_jarang@naver.com</t>
+          <t>thswltn011@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1349-6922</t>
+          <t>0507-1333-9838</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 80 504호</t>
+          <t>인천광역시 중구 영종대로 166 솔리움센텀스카이 상가 1층 107호 젤리쉬네일</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jangs_nail</t>
+          <t>https://www.instagram.com/gelish._.nail_</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7059,13 +7055,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>105</v>
+        <v>1283</v>
       </c>
       <c r="Q71" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="R71" t="n">
-        <v>111</v>
+        <v>1321</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7074,17 +7070,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1748416887</t>
+          <t>1825609603</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748416887</t>
+          <t>https://m.place.naver.com/place/1825609603</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7096,25 +7092,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ahashop nail</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>네일공간 영종하늘도시점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>odiyablog@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1486-1185</t>
+          <t>0507-1357-2207</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 옹진군 북도면 장봉로238번길 66 1층</t>
+          <t>인천광역시 중구 하늘달빛로 95 102동 108호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_gonggan1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7145,17 +7145,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7164,17 +7164,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1758864701</t>
+          <t>2006802771</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758864701</t>
+          <t>https://m.place.naver.com/place/2006802771</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7186,29 +7186,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>더리온</t>
+          <t>더네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jhjy101526@naver.com</t>
+          <t>thenail_@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>032-836-4667</t>
+          <t>0507-1481-0271</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 옹진군 백령면 백령로 282 더리온</t>
+          <t>인천광역시 중구 하늘중앙로225번길 20 215호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rPaGn</t>
+          <t>https://www.instagram.com/p/Cf_KCSIrY34/?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7234,22 +7234,22 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R73" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7258,17 +7258,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1040252234</t>
+          <t>1979788121</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040252234</t>
+          <t>https://m.place.naver.com/place/1979788121</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7280,29 +7280,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>지니네일</t>
+          <t>라르떼네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>goto_seoul@naver.com</t>
+          <t>limkyungmi10@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0507-1316-6480</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 남문안길32번길 8 2층</t>
+          <t>인천광역시 중구 하늘별빛로65번길 11 해솔프라자 403-1호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/jineenail</t>
+          <t>https://www.instagram.com/rarete_nail02</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7337,13 +7333,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="Q74" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="R74" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7352,17 +7348,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1155579596</t>
+          <t>1844112944</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155579596</t>
+          <t>https://m.place.naver.com/place/1844112944</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7374,29 +7370,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>버디네일</t>
+          <t>제이네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>hhj6910@naver.com</t>
+          <t>morningapple6@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1420-9856</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디칼 3층 309호</t>
+          <t>인천광역시 강화군 강화읍 향나무길28번길 13-1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buddy_nail__</t>
+          <t>https://www.instagram.com/j.nail_shop</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7431,13 +7423,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>620</v>
+        <v>5</v>
       </c>
       <c r="Q75" t="n">
         <v>2</v>
       </c>
       <c r="R75" t="n">
-        <v>622</v>
+        <v>7</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7446,17 +7438,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1255393282</t>
+          <t>1237271418</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1255393282</t>
+          <t>https://m.place.naver.com/place/1237271418</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7468,25 +7460,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>네일 바이 담</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sooks_room@naver.com</t>
+          <t>11dldnjs@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>032-751-6686</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 394</t>
+          <t>인천광역시 중구 햇내로13번길 17 프라임시티1차 102호 네일바이담</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nailby.dam</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7496,7 +7492,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7517,17 +7513,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>5</v>
+        <v>172</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
-        <v>9</v>
+        <v>174</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7536,17 +7532,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>36721147</t>
+          <t>1880192448</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36721147</t>
+          <t>https://m.place.naver.com/place/1880192448</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/옹진군_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/옹진군_네일샵.xlsx
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일917</t>
+          <t>네일바이에스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>nufine@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>032-751-0917</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 중구 화랑목로100번길 75 104호</t>
+          <t>인천광역시 중구 햇내로안길 14-5 102호 네일바이에스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail.917</t>
+          <t>https://www.instagram.com/nailby_s</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>439</v>
+        <v>340</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>449</v>
+        <v>343</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1363080406</t>
+          <t>1163668428</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363080406</t>
+          <t>https://m.place.naver.com/place/1163668428</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,34 +654,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미뇽네일</t>
+          <t>네일유희 하늘도시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>akstjd1018@naver.com</t>
+          <t>kim960113@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1381-9702</t>
+          <t>0507-1492-3774</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 347-1 101호</t>
+          <t>인천광역시 중구 월촌길 28 102호 네일유희</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hkxiqG</t>
+          <t>https://www.instagram.com/nailyuhee</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,7 +702,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1280952259</t>
+          <t>1310153514</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280952259</t>
+          <t>https://m.place.naver.com/place/1310153514</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,29 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일 그대와</t>
+          <t>소소네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dodo1052@naver.com</t>
+          <t>iamkimz@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1379-0491</t>
+          <t>0507-1327-9628</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 94 스타 타워1 507호</t>
+          <t>인천광역시 강화군 강화읍 강화대로404번길 9 2층 윈썸헤어&amp;소소네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.withyou</t>
+          <t>https://www.instagram.com/sosonail_y?igsh=djM3NzVmbHM5eDRo&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1267766371</t>
+          <t>1958174820</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267766371</t>
+          <t>https://m.place.naver.com/place/1958174820</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -846,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일위클로</t>
+          <t>아이온네일 인천영종점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>summerstar1984@naver.com</t>
+          <t>ym6030@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1368-4179</t>
+          <t>0507-1329-3883</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
+          <t>인천광역시 중구 영종대로196번길 15-25 운서역반도유보라퍼스트지 상가동2층226호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.weclo</t>
+          <t>https://blog.naver.com/ym6030</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>75</v>
+        <v>883</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="R5" t="n">
-        <v>76</v>
+        <v>955</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2038322752</t>
+          <t>1792903749</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038322752</t>
+          <t>https://m.place.naver.com/place/1792903749</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,34 +936,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비너스네일앤뷰티</t>
+          <t>더리온</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>jhjy101526@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1309-4148</t>
+          <t>032-836-4667</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 신문길 42 2층</t>
+          <t>인천광역시 옹진군 백령면 백령로 282 더리온</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/venus_nail4148</t>
+          <t>http://pf.kakao.com/_rPaGn</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -988,22 +984,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1141156599</t>
+          <t>1040252234</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141156599</t>
+          <t>https://m.place.naver.com/place/1040252234</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오앤오네일</t>
+          <t>뉴얼리네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bliss-mj@naver.com</t>
+          <t>kimaechin01@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1319-2481</t>
+          <t>0507-1429-1729</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 88 7층 701호</t>
+          <t>인천광역시 강화군 선원면 중앙로 162-31 서희스타힐스 106동 1층 상가</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ono__nail_studio</t>
+          <t>https://www.instagram.com/nurely_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R7" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2034560142</t>
+          <t>2009541921</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2034560142</t>
+          <t>https://m.place.naver.com/place/2009541921</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1128,25 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일오다</t>
+          <t>프프네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jin568900@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1407-8841</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 28 그랑블루인영종 209호</t>
+          <t>인천광역시 강화군 강화읍 남문안길 5-1 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.oda</t>
+          <t>https://www.instagram.com/ff__nail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>243</v>
+        <v>7</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1153727265</t>
+          <t>1170338521</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153727265</t>
+          <t>https://m.place.naver.com/place/1170338521</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아이온네일 인천영종점</t>
+          <t>네일핫플</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ym6030@naver.com</t>
+          <t>dydals1wj@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1329-3883</t>
+          <t>032-747-0321</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로196번길 15-25 운서역반도유보라퍼스트지 상가동2층226호</t>
+          <t>인천광역시 중구 자연대로 38 208호 네일핫플</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ym6030</t>
+          <t>https://www.instagram.com/nail_hotple?igsh=MTl4dmd6ZGdlcHF4dA==</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1266,7 +1266,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>885</v>
+        <v>176</v>
       </c>
       <c r="Q9" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>957</v>
+        <v>181</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1792903749</t>
+          <t>1813910551</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792903749</t>
+          <t>https://m.place.naver.com/place/1813910551</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일이안</t>
+          <t>달빛네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wjstngusrn@naver.com</t>
+          <t>youwool1004@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1467-1252</t>
+          <t>0507-1316-8875</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 47 610호</t>
+          <t>인천광역시 강화군 강화읍 강화대로 310 201호 달빛네일</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ian</t>
+          <t>https://open.kakao.com/o/sLs1Sagi</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1360,7 +1360,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1117993147</t>
+          <t>2052753261</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117993147</t>
+          <t>https://m.place.naver.com/place/2052753261</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1406,44 +1406,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아하뷰티샵</t>
+          <t>더네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ahasoft_crm@naver.com</t>
+          <t>thenail7282@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1366-0805</t>
+          <t>0507-1481-0271</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 옹진군 북도면 장봉로238번길 66</t>
+          <t>인천광역시 중구 하늘중앙로225번길 20 215호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/p/Cf_KCSIrY34/?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1459,17 +1459,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1135765422</t>
+          <t>1979788121</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135765422</t>
+          <t>https://m.place.naver.com/place/1979788121</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1500,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>라비쥬</t>
+          <t>오니네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sincity01@naver.com</t>
+          <t>wjsska1907@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1340-8384</t>
+          <t>0507-1311-0663</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 15 세영프라자 4층</t>
+          <t>인천광역시 강화군 강화읍 갑룡길 29 1층, 카페88 내부위치</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://instagram.com/salon_labijou</t>
+          <t>http://instagram.com/oninail_</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>332</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
-        <v>403</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>735</v>
+        <v>12</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>37064341</t>
+          <t>1245994155</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37064341</t>
+          <t>https://m.place.naver.com/place/1245994155</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1594,25 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일은영</t>
+          <t>네일위클로</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>naileun_0@naver.com</t>
+          <t>summerstar1984@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1368-4179</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 45 118호</t>
+          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://instagram.com/naileun_0</t>
+          <t>https://www.instagram.com/nail.weclo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1647,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>375</v>
+        <v>80</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1430851204</t>
+          <t>2038322752</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430851204</t>
+          <t>https://m.place.naver.com/place/2038322752</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1688,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>옥스네일</t>
+          <t>두손네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>odiyablog@naver.com</t>
+          <t>doosonnail@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1434-0166</t>
+          <t>0507-1401-4970</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 139 777동(센텀베뉴 정문상가내) 103-2호</t>
+          <t>인천광역시 중구 흰바위로 31 에어로시티</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ok_s_nail</t>
+          <t>https://www.instagram.com/jangjeongsnyi/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1741,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="R14" t="n">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2011391847</t>
+          <t>125000879</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011391847</t>
+          <t>https://m.place.naver.com/place/125000879</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1782,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일,윤</t>
+          <t>태봉씨뷰티살롱&amp;LCN공식 인증매장</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>songyum84@naver.com</t>
+          <t>xogns07@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1355-0330</t>
+          <t>0507-1330-1831</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 37 2층 2호</t>
+          <t>인천광역시 중구 하늘중앙로225번길 20 9층 910호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/xogns07</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1810,12 +1814,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1831,17 +1835,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>19</v>
+        <v>455</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="R15" t="n">
-        <v>19</v>
+        <v>568</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2000502238</t>
+          <t>1381683377</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000502238</t>
+          <t>https://m.place.naver.com/place/1381683377</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1872,29 +1876,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>루시네일</t>
+          <t>네일 또 보니</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dkfma2329@naver.com</t>
+          <t>yellowground_@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1321-0922</t>
+          <t>0507-1355-4749</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 40 비젼프라자2 509호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 18 효정타워 305호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lllucynail_</t>
+          <t>https://www.instagram.com/nail_ddoboni</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1929,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>338</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>691165364</t>
+          <t>1350394025</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/691165364</t>
+          <t>https://m.place.naver.com/place/1350394025</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1966,29 +1970,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>쟝스네일</t>
+          <t>네일,빛</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lee_jarang@naver.com</t>
+          <t>ekeor0718@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1349-6922</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 80 504호</t>
+          <t>인천광역시 중구 하늘중앙로 193 조양타워 4층 409호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jangs_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2019,17 +2019,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1748416887</t>
+          <t>1646288604</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748416887</t>
+          <t>https://m.place.naver.com/place/1646288604</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2060,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일, 피어나</t>
+          <t>네일 그대와</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bbang52@naver.com</t>
+          <t>dodo1052@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1365-4941</t>
+          <t>0507-1379-0491</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 193 314호</t>
+          <t>인천광역시 중구 하늘달빛로 94 스타 타워1 507호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fe_ar_not/</t>
+          <t>https://www.instagram.com/nail._.withyou</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1581968497</t>
+          <t>1267766371</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581968497</t>
+          <t>https://m.place.naver.com/place/1267766371</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2154,25 +2154,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>그리닷뷰티</t>
+          <t>네일은빛나</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dean0707@naver.com</t>
+          <t>raronail@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1375-7181</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
+          <t>인천광역시 중구 영종대로196번길 15-25 반도유보라퍼스티지 상가동 1층 109호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_by_shine</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2182,7 +2186,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2203,17 +2207,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2226,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1208135114</t>
+          <t>1399161803</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208135114</t>
+          <t>https://m.place.naver.com/place/1399161803</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2244,29 +2248,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>그릿네일</t>
+          <t>퐁네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>grit_nail@naver.com</t>
+          <t>yegi1929@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1464-3789</t>
+          <t>0507-1340-7654</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디컬 2층 202호</t>
+          <t>인천광역시 중구 하늘달빛로 90-7 스카이에비뉴1 (6층)아띠스윤 내</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/grit.nail</t>
+          <t>http://www.instagram.com/_pongnail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2301,13 +2305,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="Q20" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="R20" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2320,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1981189370</t>
+          <t>1591123938</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1981189370</t>
+          <t>https://m.place.naver.com/place/1591123938</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2338,29 +2342,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>레푸스 강화점</t>
+          <t>원네일앤뷰티 영종하늘도시점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>refuss_ganghwa@naver.com</t>
+          <t>wonnail0929@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1409-2278</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 충렬사로 25 남산빌딩 2층 202호</t>
+          <t>인천광역시 중구 하늘달빛로 70 메디피아빌딩 304호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@강화레푸스</t>
+          <t>https://blog.naver.com/wonnail0929</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>19</v>
+        <v>196</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R21" t="n">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2410,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1506333714</t>
+          <t>1259164731</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1506333714</t>
+          <t>https://m.place.naver.com/place/1259164731</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2432,29 +2432,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>태봉씨뷰티살롱&amp;LCN공식 인증매장</t>
+          <t>템팅네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>xogns07@naver.com</t>
+          <t>withkyra@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1330-1831</t>
+          <t>0507-1398-4155</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 20 9층 910호</t>
+          <t>인천광역시 중구 햇내로안길 18-4 1층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xogns07</t>
+          <t>https://www.instagram.com/tempting_nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>455</v>
+        <v>280</v>
       </c>
       <c r="Q22" t="n">
-        <v>113</v>
+        <v>6</v>
       </c>
       <c r="R22" t="n">
-        <v>568</v>
+        <v>286</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2504,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1381683377</t>
+          <t>1951261120</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381683377</t>
+          <t>https://m.place.naver.com/place/1951261120</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2526,34 +2526,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>슈가네일</t>
+          <t>그릿네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>junge1004j@naver.com</t>
+          <t>grit_nail@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1406-0391</t>
+          <t>0507-1464-3789</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 36 영종주공스카이빌아파트 상가 103호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디컬 2층 202호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xlLxmyn</t>
+          <t>https://www.instagram.com/grit.nail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2574,7 +2574,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="R23" t="n">
-        <v>173</v>
+        <v>230</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2598,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1533004146</t>
+          <t>1981189370</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533004146</t>
+          <t>https://m.place.naver.com/place/1981189370</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2620,29 +2620,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>그때 그 네일</t>
+          <t>네일 바이 담</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>goodbyealice@naver.com</t>
+          <t>11dldnjs@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1301-9627</t>
+          <t>032-751-6686</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호</t>
+          <t>인천광역시 중구 햇내로13번길 17 프라임시티1차 102호 네일바이담</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ggnail</t>
+          <t>http://www.instagram.com/nailby.dam</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2692,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1380919881</t>
+          <t>1880192448</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1380919881</t>
+          <t>https://m.place.naver.com/place/1880192448</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2714,29 +2714,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>달빛네일</t>
+          <t>그때 그 네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>duoshan_sz@naver.com</t>
+          <t>goodbyealice@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1316-8875</t>
+          <t>0507-1301-9627</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 310 201호 달빛네일</t>
+          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sLs1Sagi</t>
+          <t>https://www.instagram.com/_ggnail</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2762,7 +2762,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>139</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2786,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2052753261</t>
+          <t>1380919881</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2052753261</t>
+          <t>https://m.place.naver.com/place/1380919881</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2808,25 +2808,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일바이에스</t>
+          <t>압구정네일샵</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nufine@naver.com</t>
+          <t>bitna0614@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>032-751-0401</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로안길 14-5 102호 네일바이에스</t>
+          <t>인천광역시 중구 운남로 158 2층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailby_s</t>
+          <t>https://www.instagram.com/agn0401/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2861,13 +2865,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>340</v>
+        <v>18</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>343</v>
+        <v>18</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2880,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1163668428</t>
+          <t>414262111</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163668428</t>
+          <t>https://m.place.naver.com/place/414262111</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2902,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
+          <t>그리닷뷰티</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>vizarai@naver.com</t>
+          <t>dean0707@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0507-1327-8743</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 14 301호 네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
+          <t>인천광역시 중구 하늘중앙로225번길 12 701호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vizarai</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>243</v>
+        <v>34</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>256</v>
+        <v>34</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +2970,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1976884898</t>
+          <t>1208135114</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976884898</t>
+          <t>https://m.place.naver.com/place/1208135114</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2992,25 +2992,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>원네일앤뷰티 영종하늘도시점</t>
+          <t>네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wonnail0929@naver.com</t>
+          <t>vizarai@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1327-8743</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 70 메디피아빌딩 304호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 14 301호 네일뷰티홀릭&amp;오로지푸스 인천영종점</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wonnail0929</t>
+          <t>https://blog.naver.com/vizarai</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3045,13 +3049,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="R28" t="n">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3060,17 +3064,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1259164731</t>
+          <t>1976884898</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259164731</t>
+          <t>https://m.place.naver.com/place/1976884898</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3082,34 +3086,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>템팅네일</t>
+          <t>네일 두나</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>withkyra@naver.com</t>
+          <t>juvide@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1398-4155</t>
+          <t>0507-1314-5785</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로안길 18-4 1층</t>
+          <t>인천광역시 중구 두미포로 60 101호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tempting_nail</t>
+          <t>https://pf.kakao.com/_XVSxbn</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3130,7 +3134,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3139,13 +3143,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3154,17 +3158,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1951261120</t>
+          <t>1880658481</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1951261120</t>
+          <t>https://m.place.naver.com/place/1880658481</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3176,29 +3180,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>주드네일</t>
+          <t>무</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>luv_gayeon0@naver.com</t>
+          <t>sooks_room@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1397-7996</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 82 4층 405호</t>
+          <t>인천광역시 강화군 강화읍 강화대로 394</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/luv_gayeon0</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3229,17 +3229,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>460</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>482</v>
+        <v>8</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,17 +3248,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1740443365</t>
+          <t>36721147</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1740443365</t>
+          <t>https://m.place.naver.com/place/36721147</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3270,25 +3270,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>오늘네일샵</t>
+          <t>네일바유</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>webmaia21@naver.com</t>
+          <t>fhwmay@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1414-0777</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>충청남도 서산시 대산읍 충의로 1889</t>
+          <t>인천광역시 중구 흰바위로 258 센타프라자 2층 208호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://instagram.com/_nail_2day</t>
+          <t>https://www.instagram.com/nail._.bayu</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3323,13 +3327,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>290</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>295</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,17 +3342,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1283160281</t>
+          <t>1489158637</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283160281</t>
+          <t>https://m.place.naver.com/place/1489158637</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3360,29 +3364,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>언니네일 페디베네 영종 운서점</t>
+          <t>네일은영</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>botong56@naver.com</t>
+          <t>naileun_0@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1416-6632</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 중구 넙디로 47 백산빌딩 103호 언니네일 페디베네 영종 운서점</t>
+          <t>인천광역시 중구 흰바위로 45 118호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/botong56</t>
+          <t>http://instagram.com/naileun_0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3417,13 +3417,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>141</v>
+        <v>376</v>
       </c>
       <c r="Q32" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="R32" t="n">
-        <v>205</v>
+        <v>382</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,17 +3432,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>37101621</t>
+          <t>1430851204</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37101621</t>
+          <t>https://m.place.naver.com/place/1430851204</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3454,29 +3454,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>블랑디에 네일</t>
+          <t>네일, 피어나</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>gkgmlwn2929@naver.com</t>
+          <t>bbang52@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1393-2128</t>
+          <t>0507-1365-4941</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 7-15 디에스지타워 10층 1003호</t>
+          <t>인천광역시 중구 하늘중앙로 193 314호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/blancdrenail</t>
+          <t>https://www.instagram.com/fe_ar_not/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3502,7 +3502,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>302</v>
+        <v>54</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>304</v>
+        <v>55</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,17 +3526,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1984068599</t>
+          <t>1581968497</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1984068599</t>
+          <t>https://m.place.naver.com/place/1581968497</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3548,25 +3548,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ahashop nail</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>네일파르크</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>liphop2588@naver.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1486-1185</t>
+          <t>0507-1385-0712</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 옹진군 북도면 장봉로238번길 66 1층</t>
+          <t>인천광역시 중구 화랑목로 50-7 102호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_parc</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3576,7 +3580,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3597,17 +3601,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,17 +3620,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1758864701</t>
+          <t>1965314720</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758864701</t>
+          <t>https://m.place.naver.com/place/1965314720</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3638,29 +3642,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>소소네일</t>
+          <t>네일공간 영종하늘도시점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>iamkimz@naver.com</t>
+          <t>odiyablog@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1327-9628</t>
+          <t>0507-1357-2207</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로404번길 9 2층 윈썸헤어&amp;소소네일</t>
+          <t>인천광역시 중구 하늘달빛로 95 102동 108호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sosonail_y?igsh=djM3NzVmbHM5eDRo&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_gonggan1</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3695,13 +3699,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,17 +3714,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1958174820</t>
+          <t>2006802771</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958174820</t>
+          <t>https://m.place.naver.com/place/2006802771</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3732,29 +3736,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일은빛나</t>
+          <t>네일더스킨</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>raronail@naver.com</t>
+          <t>feel3051@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1375-7181</t>
+          <t>0507-1411-0441</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로196번길 15-25 반도유보라퍼스티지 상가동 1층 109호</t>
+          <t>인천광역시 중구 흰바위로 258 211호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_by_shine</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3764,7 +3768,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3785,17 +3789,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3804,17 +3808,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1399161803</t>
+          <t>1314782883</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399161803</t>
+          <t>https://m.place.naver.com/place/1314782883</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3826,29 +3830,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>도도네일</t>
+          <t>그레이스네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mh95577@naver.com</t>
+          <t>smsy7784@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1405-5840</t>
+          <t>0507-1379-5084</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 중구 두미포로 89 102호</t>
+          <t>인천광역시 강화군 강화읍 강화대로248번길 24 갑룡프라자 2층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/dodonail.2024</t>
+          <t>https://www.instagram.com/grace_nail_?igsh=eGhhYXZlaGl0Z3hh&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3883,13 +3887,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>239</v>
+        <v>159</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>245</v>
+        <v>160</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3898,17 +3902,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>38321738</t>
+          <t>1030374689</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38321738</t>
+          <t>https://m.place.naver.com/place/1030374689</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3920,29 +3924,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>두손네일</t>
+          <t>네일917</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>doosonnail@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1401-4970</t>
+          <t>032-751-0917</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 31 에어로시티</t>
+          <t>인천광역시 중구 화랑목로100번길 75 104호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jangjeongsnyi/</t>
+          <t>http://www.instagram.com/nail.917</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3977,13 +3981,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>7</v>
+        <v>439</v>
       </c>
       <c r="Q38" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="R38" t="n">
-        <v>68</v>
+        <v>449</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,17 +3996,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>125000879</t>
+          <t>1363080406</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/125000879</t>
+          <t>https://m.place.naver.com/place/1363080406</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4014,34 +4018,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일 두나</t>
+          <t>쏘니네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pooglemom@naver.com</t>
+          <t>ultramariine@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1314-5785</t>
+          <t>0507-1485-3336</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 중구 두미포로 60 101호</t>
+          <t>인천광역시 중구 흰바위로 284 110-1호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_XVSxbn</t>
+          <t>https://www.instagram.com/ssoninail</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4062,7 +4066,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4071,13 +4075,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,17 +4090,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1880658481</t>
+          <t>1226536825</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880658481</t>
+          <t>https://m.place.naver.com/place/1226536825</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4108,29 +4112,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>더 트윙클 네일</t>
+          <t>이뽐뷰티 강화점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>doll_a_wh@naver.com</t>
+          <t>leebbom_kh@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1488-2043</t>
+          <t>0507-1385-2307</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 262 럭키프라자 305호</t>
+          <t>인천광역시 강화군 강화읍 동문안길 7 B동 101호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the.twinkle_nail1</t>
+          <t>https://blog.naver.com/leebbom_kh</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4145,7 +4149,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4165,13 +4169,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>414</v>
+        <v>101</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R40" t="n">
-        <v>420</v>
+        <v>115</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,17 +4184,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1809066919</t>
+          <t>1404657024</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1809066919</t>
+          <t>https://m.place.naver.com/place/1404657024</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4202,29 +4206,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>블라썸뷰티 동성제약 풀리메디 영종점</t>
+          <t>비너스네일앤뷰티</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>yanstar80@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1303-3553</t>
+          <t>0507-1309-4148</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 중구 모랫말로 6-9 101호</t>
+          <t>인천광역시 강화군 강화읍 신문길 42 2층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://instagram.com/blossom_btl</t>
+          <t>https://www.instagram.com/venus_nail4148</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4259,13 +4263,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>409</v>
+        <v>24</v>
       </c>
       <c r="Q41" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>884</v>
+        <v>24</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,17 +4278,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1867109358</t>
+          <t>1141156599</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867109358</t>
+          <t>https://m.place.naver.com/place/1141156599</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4296,29 +4300,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일유희 하늘도시</t>
+          <t>레푸스 강화점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kim960113@naver.com</t>
+          <t>refuss_ganghwa@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1492-3774</t>
+          <t>0507-1409-2278</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 중구 월촌길 28 102호 네일유희</t>
+          <t>인천광역시 강화군 강화읍 충렬사로 25 남산빌딩 2층 202호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailyuhee</t>
+          <t>https://www.youtube.com/@강화레푸스</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4333,7 +4337,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4353,13 +4357,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4368,17 +4372,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1310153514</t>
+          <t>1506333714</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1310153514</t>
+          <t>https://m.place.naver.com/place/1506333714</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4390,29 +4394,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일파르크</t>
+          <t>쟝스네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>liphop2588@naver.com</t>
+          <t>lee_jarang@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1385-0712</t>
+          <t>0507-1349-6922</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 중구 화랑목로 50-7 102호</t>
+          <t>인천광역시 중구 하늘달빛로 80 504호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_parc</t>
+          <t>https://www.instagram.com/jangs_nail</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4447,13 +4451,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="R43" t="n">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4462,17 +4466,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1965314720</t>
+          <t>1748416887</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965314720</t>
+          <t>https://m.place.naver.com/place/1748416887</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4484,29 +4488,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>프프네일</t>
+          <t>더 트윙클 네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>doll_a_wh@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1407-8841</t>
+          <t>0507-1488-2043</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 남문안길 5-1 1층</t>
+          <t>인천광역시 중구 흰바위로 262 럭키프라자 305호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ff__nail</t>
+          <t>https://www.instagram.com/the.twinkle_nail1</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4541,13 +4545,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R44" t="n">
-        <v>7</v>
+        <v>422</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,17 +4560,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1170338521</t>
+          <t>1809066919</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1170338521</t>
+          <t>https://m.place.naver.com/place/1809066919</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4578,34 +4582,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>오니네일</t>
+          <t>네일했냥</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>wjsska1907@naver.com</t>
+          <t>nababa33@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1311-0663</t>
+          <t>0507-1346-6543</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 갑룡길 29 1층, 카페88 내부위치</t>
+          <t>인천광역시 중구 하늘달빛로 90-27 109호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://instagram.com/oninail_</t>
+          <t>http://pf.kakao.com/_PxiixmG</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4626,7 +4630,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4635,13 +4639,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>6</v>
+        <v>1518</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="R45" t="n">
-        <v>12</v>
+        <v>1584</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,17 +4654,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1245994155</t>
+          <t>1874909116</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245994155</t>
+          <t>https://m.place.naver.com/place/1874909116</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4672,44 +4676,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>바비수네일&amp;태닝</t>
+          <t>더예쁨네일피부</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>vavisu_nail@naver.com</t>
+          <t>tlsrl0104@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>032-752-8700</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 94 스타타워 407호</t>
+          <t>인천광역시 중구 자연대로 37 스카이가든 2층 206호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vavisu_nail</t>
+          <t>https://www.theyepm.com</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4725,17 +4725,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4744,17 +4744,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>35516411</t>
+          <t>2044624904</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35516411</t>
+          <t>https://m.place.naver.com/place/2044624904</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4766,29 +4766,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일바유</t>
+          <t>도도네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>fhwmay@naver.com</t>
+          <t>dutjdgml70@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1414-0777</t>
+          <t>0507-1405-5840</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 258 센타프라자 2층 208호</t>
+          <t>인천광역시 중구 두미포로 89 102호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.bayu</t>
+          <t>http://www.instagram.com/dodonail.2024</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4823,13 +4823,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R47" t="n">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4838,17 +4838,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1489158637</t>
+          <t>38321738</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1489158637</t>
+          <t>https://m.place.naver.com/place/38321738</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4860,29 +4860,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>스튜디오공감</t>
+          <t>아하뷰티샵</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>studi5gonggam_art@naver.com</t>
+          <t>ahasoft_crm@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1380-0311</t>
+          <t>0507-1366-0805</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호 스튜디오공감</t>
+          <t>인천광역시 옹진군 북도면 장봉로238번길 66</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/studi5gonggam_art</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4913,17 +4913,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>206</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>219</v>
+        <v>1</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1085588496</t>
+          <t>1135765422</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1085588496</t>
+          <t>https://m.place.naver.com/place/1135765422</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4954,29 +4954,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>레푸스 인천영종점</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>lje9539@naver.com</t>
-        </is>
-      </c>
+          <t>ahashop nail</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1497-0007</t>
+          <t>0507-1486-1185</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로 100 신성하우스빌 3층 301호</t>
+          <t>인천광역시 옹진군 북도면 장봉로238번길 66 1층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_heyazi/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4986,7 +4982,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5007,17 +5003,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5026,17 +5022,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1131150431</t>
+          <t>1758864701</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131150431</t>
+          <t>https://m.place.naver.com/place/1758864701</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5048,29 +5044,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>플레이버네일</t>
+          <t>블라썸뷰티 동성제약 풀리메디 영종점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>oao08@naver.com</t>
+          <t>yanstar80@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1382-0428</t>
+          <t>0507-1303-3553</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 중구 운서로7번길 60 1층 103호</t>
+          <t>인천광역시 중구 모랫말로 6-9 101호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flavornail?igsh=MWgwY3luaWppNHdtZg%3D%3D&amp;utm_source=qr</t>
+          <t>http://instagram.com/blossom_btl</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5105,13 +5101,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>257</v>
+        <v>409</v>
       </c>
       <c r="Q50" t="n">
-        <v>3</v>
+        <v>475</v>
       </c>
       <c r="R50" t="n">
-        <v>260</v>
+        <v>884</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5120,17 +5116,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1693860525</t>
+          <t>1867109358</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693860525</t>
+          <t>https://m.place.naver.com/place/1867109358</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5142,39 +5138,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>더리온</t>
+          <t>루비네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jhjy101526@naver.com</t>
+          <t>ruby1004_mj@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>032-836-4667</t>
+          <t>0507-1342-4252</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 옹진군 백령면 백령로 282 더리온</t>
+          <t>인천광역시 강화군 강화읍 중앙로 68 하나로마트 2층 214호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rPaGn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5190,7 +5186,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5199,13 +5195,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5214,17 +5210,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1040252234</t>
+          <t>1791159276</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040252234</t>
+          <t>https://m.place.naver.com/place/1791159276</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5236,25 +5232,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>N.Nail</t>
+          <t>옥스네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nailon22@naver.com</t>
+          <t>odiyablog@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1434-0166</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 8 207호(운서동, 프라임시티3)</t>
+          <t>인천광역시 중구 하늘달빛로 139 777동(센텀베뉴 정문상가내) 103-2호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.nail_3/</t>
+          <t>https://www.instagram.com/ok_s_nail</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5289,13 +5289,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="R52" t="n">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2001565256</t>
+          <t>2011391847</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001565256</t>
+          <t>https://m.place.naver.com/place/2011391847</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5326,25 +5326,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>루비네일</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>지니네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>goto_seoul@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1342-4252</t>
+          <t>0507-1316-6480</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 중앙로 68 하나로마트 2층 214호</t>
+          <t>인천광역시 강화군 강화읍 남문안길32번길 8 2층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/jineenail</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5354,7 +5358,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5375,17 +5379,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5394,17 +5398,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1791159276</t>
+          <t>1155579596</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1791159276</t>
+          <t>https://m.place.naver.com/place/1155579596</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5416,25 +5420,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>퐁네일</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>바비수네일&amp;태닝</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>vavisu_nail@naver.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1340-7654</t>
+          <t>032-752-8700</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 90-7 스카이에비뉴1 (6층)아띠스윤 내</t>
+          <t>인천광역시 중구 하늘달빛로 94 스타타워 407호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_pongnail</t>
+          <t>https://blog.naver.com/vavisu_nail</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5449,7 +5457,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5465,17 +5473,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="R54" t="n">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5484,17 +5492,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1591123938</t>
+          <t>35516411</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1591123938</t>
+          <t>https://m.place.naver.com/place/35516411</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5506,29 +5514,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>쏘니네일</t>
+          <t>블랑디에 네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ultramariine@naver.com</t>
+          <t>gkgmlwn2929@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1485-3336</t>
+          <t>0507-1393-2128</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 284 110-1호</t>
+          <t>인천광역시 중구 하늘별빛로65번길 7-15 디에스지타워 10층 1003호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssoninail</t>
+          <t>https://www.instagram.com/blancdrenail</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5554,7 +5562,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5563,13 +5571,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>13</v>
+        <v>302</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>14</v>
+        <v>304</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5578,17 +5586,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1226536825</t>
+          <t>1984068599</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226536825</t>
+          <t>https://m.place.naver.com/place/1984068599</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5600,29 +5608,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일더스킨</t>
+          <t>플레이버네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>feel3051@naver.com</t>
+          <t>oao08@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1411-0441</t>
+          <t>0507-1382-0428</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 258 211호</t>
+          <t>인천광역시 중구 운서로7번길 60 1층 103호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/flavornail?igsh=MWgwY3luaWppNHdtZg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5632,7 +5640,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5653,17 +5661,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5672,17 +5680,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1314782883</t>
+          <t>1693860525</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314782883</t>
+          <t>https://m.place.naver.com/place/1693860525</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5694,12 +5702,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>더예쁨네일피부</t>
+          <t>네일오다</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>tlsrl0104@naver.com</t>
+          <t>jin568900@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -5707,22 +5715,22 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 37 스카이가든 2층 206호</t>
+          <t>인천광역시 중구 자연대로 28 그랑블루인영종 209호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.theyepm.com</t>
+          <t>https://www.instagram.com/nail.oda</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5747,13 +5755,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R57" t="n">
-        <v>83</v>
+        <v>246</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5762,17 +5770,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2044624904</t>
+          <t>1153727265</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044624904</t>
+          <t>https://m.place.naver.com/place/1153727265</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5784,30 +5792,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>가디스뷰티샵</t>
+          <t>미뇽네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>goddess503@naver.com</t>
+          <t>akstjd1018@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1381-9702</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 7-9 스카이타워5층 503호</t>
+          <t>인천광역시 강화군 강화읍 강화대로 347-1 101호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goddess503</t>
+          <t>http://pf.kakao.com/_hkxiqG</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5817,7 +5829,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5828,7 +5840,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5837,13 +5849,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5852,17 +5864,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1848560502</t>
+          <t>1280952259</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1848560502</t>
+          <t>https://m.place.naver.com/place/1280952259</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5874,29 +5886,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>압구정네일샵</t>
+          <t>가디스뷰티샵</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>bitna0614@naver.com</t>
+          <t>goddess503@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>032-751-0401</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 중구 운남로 158 2층</t>
+          <t>인천광역시 중구 하늘별빛로65번길 7-9 스카이타워5층 503호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agn0401/</t>
+          <t>https://blog.naver.com/goddess503</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5911,7 +5919,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5931,13 +5939,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R59" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5946,17 +5954,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>414262111</t>
+          <t>1848560502</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/414262111</t>
+          <t>https://m.place.naver.com/place/1848560502</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5968,29 +5976,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>지니네일</t>
+          <t>네일,윤</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>goto_seoul@naver.com</t>
+          <t>yeseuldp@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1316-6480</t>
+          <t>0507-1355-0330</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 남문안길32번길 8 2층</t>
+          <t>인천광역시 중구 자연대로 37 2층 2호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/jineenail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6000,7 +6008,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6021,17 +6029,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6040,17 +6048,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1155579596</t>
+          <t>2000502238</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155579596</t>
+          <t>https://m.place.naver.com/place/2000502238</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6062,29 +6070,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>이뽐뷰티 강화점</t>
+          <t>라르떼네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>leebbom_kh@naver.com</t>
+          <t>limkyungmi10@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0507-1385-2307</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 동문안길 7 B동 101호</t>
+          <t>인천광역시 중구 하늘별빛로65번길 11 해솔프라자 403-1호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leebbom_kh</t>
+          <t>https://www.instagram.com/rarete_nail02</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6099,7 +6103,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6119,13 +6123,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R61" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6134,17 +6138,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1404657024</t>
+          <t>1844112944</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404657024</t>
+          <t>https://m.place.naver.com/place/1844112944</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6156,29 +6160,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>버디네일</t>
+          <t>오앤오네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>hhj6910@naver.com</t>
+          <t>bliss-mj@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1420-9856</t>
+          <t>0507-1319-2481</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디칼 3층 309호</t>
+          <t>인천광역시 중구 하늘달빛로 88 7층 701호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buddy_nail__</t>
+          <t>https://www.instagram.com/ono__nail_studio</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6213,13 +6217,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>621</v>
+        <v>96</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>623</v>
+        <v>97</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6228,17 +6232,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1255393282</t>
+          <t>2034560142</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1255393282</t>
+          <t>https://m.place.naver.com/place/2034560142</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6250,29 +6254,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일핫플</t>
+          <t>퍼플리네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>dydals1wj@naver.com</t>
+          <t>u_un0709@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>032-747-0321</t>
+          <t>0507-1315-4140</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자연대로 38 208호 네일핫플</t>
+          <t>인천광역시 강화군 선원면 중앙로 162-3 2층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_hotple?igsh=MTl4dmd6ZGdlcHF4dA==</t>
+          <t>https://www.instagram.com/purply._.nail/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6298,7 +6302,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6307,13 +6311,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>175</v>
+        <v>41</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6322,17 +6326,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1813910551</t>
+          <t>2094549338</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1813910551</t>
+          <t>https://m.place.naver.com/place/2094549338</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6344,34 +6348,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>뉴얼리네일</t>
+          <t>슈가네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kimaechin01@naver.com</t>
+          <t>junge1004j@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1429-1729</t>
+          <t>0507-1406-0391</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 선원면 중앙로 162-31 서희스타힐스 106동 1층 상가</t>
+          <t>인천광역시 중구 흰바위로 36 영종주공스카이빌아파트 상가 103호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nurely_nail</t>
+          <t>https://pf.kakao.com/_xlLxmyn</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6392,7 +6396,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6401,13 +6405,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>27</v>
+        <v>169</v>
       </c>
       <c r="Q64" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>40</v>
+        <v>173</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6416,17 +6420,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2009541921</t>
+          <t>1533004146</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009541921</t>
+          <t>https://m.place.naver.com/place/1533004146</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6438,29 +6442,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일 또 보니</t>
+          <t>N.Nail</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>yellowground_@naver.com</t>
+          <t>nailon22@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0507-1355-4749</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로195번길 18 효정타워 305호</t>
+          <t>인천광역시 중구 햇내로13번길 8 207호(운서동, 프라임시티3)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ddoboni</t>
+          <t>https://www.instagram.com/n.nail_3/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6495,13 +6495,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>328</v>
+        <v>10</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>338</v>
+        <v>11</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6510,17 +6510,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1350394025</t>
+          <t>2001565256</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350394025</t>
+          <t>https://m.place.naver.com/place/2001565256</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6532,29 +6532,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>그레이스네일</t>
+          <t>라비쥬</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>lumirode@naver.com</t>
+          <t>sincity01@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1379-5084</t>
+          <t>0507-1340-8384</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로248번길 24 갑룡프라자 2층</t>
+          <t>인천광역시 중구 하늘중앙로195번길 15 세영프라자 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/grace_nail_?igsh=eGhhYXZlaGl0Z3hh&amp;utm_source=qr</t>
+          <t>http://instagram.com/salon_labijou</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6589,13 +6589,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>159</v>
+        <v>332</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="R66" t="n">
-        <v>160</v>
+        <v>735</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6604,17 +6604,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1030374689</t>
+          <t>37064341</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030374689</t>
+          <t>https://m.place.naver.com/place/37064341</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6626,29 +6626,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>엔샵</t>
+          <t>언니네일 페디베네 영종 운서점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jiansritual@naver.com</t>
+          <t>botong56@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1404-6421</t>
+          <t>0507-1416-6632</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 19 센타프라자 203호</t>
+          <t>인천광역시 중구 넙디로 47 백산빌딩 103호 언니네일 페디베네 영종 운서점</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jiansritual</t>
+          <t>https://blog.naver.com/botong56</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="Q67" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="R67" t="n">
-        <v>5</v>
+        <v>205</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6698,17 +6698,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>34362707</t>
+          <t>37101621</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34362707</t>
+          <t>https://m.place.naver.com/place/37101621</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6720,34 +6720,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일했냥</t>
+          <t>스튜디오공감</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>mementomori-24@naver.com</t>
+          <t>studi5gonggam_art@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1346-6543</t>
+          <t>0507-1380-0311</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 90-27 109호</t>
+          <t>인천광역시 중구 햇내로13번길 8 프라임시티3차 201호 스튜디오공감</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_PxiixmG</t>
+          <t>https://blog.naver.com/studi5gonggam_art</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6768,7 +6768,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6777,13 +6777,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1518</v>
+        <v>206</v>
       </c>
       <c r="Q68" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="R68" t="n">
-        <v>1584</v>
+        <v>219</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1874909116</t>
+          <t>1085588496</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874909116</t>
+          <t>https://m.place.naver.com/place/1085588496</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6814,25 +6814,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일,빛</t>
+          <t>루시네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ekeor0718@naver.com</t>
+          <t>dkfma2329@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1321-0922</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로 193 조양타워 4층 409호</t>
+          <t>인천광역시 중구 자연대로 40 비젼프라자2 509호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lllucynail_</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6842,7 +6846,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6863,17 +6867,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R69" t="n">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6882,17 +6886,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1646288604</t>
+          <t>691165364</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1646288604</t>
+          <t>https://m.place.naver.com/place/691165364</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6904,29 +6908,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>퍼플리네일</t>
+          <t>제이네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>u_un0709@naver.com</t>
+          <t>morningapple6@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0507-1315-4140</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 선원면 중앙로 162-3 2층</t>
+          <t>인천광역시 강화군 강화읍 향나무길28번길 13-1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/purply._.nail/</t>
+          <t>https://www.instagram.com/j.nail_shop</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6976,17 +6976,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2094549338</t>
+          <t>1237271418</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094549338</t>
+          <t>https://m.place.naver.com/place/1237271418</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7055,13 +7055,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="Q71" t="n">
         <v>38</v>
       </c>
       <c r="R71" t="n">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7092,29 +7092,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일공간 영종하늘도시점</t>
+          <t>주드네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>odiyablog@naver.com</t>
+          <t>luv_gayeon0@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1357-2207</t>
+          <t>0507-1397-7996</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘달빛로 95 102동 108호</t>
+          <t>인천광역시 중구 하늘달빛로 82 4층 405호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_gonggan1</t>
+          <t>https://blog.naver.com/luv_gayeon0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7149,13 +7149,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>24</v>
+        <v>462</v>
       </c>
       <c r="Q72" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="R72" t="n">
-        <v>33</v>
+        <v>484</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7164,17 +7164,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2006802771</t>
+          <t>1740443365</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2006802771</t>
+          <t>https://m.place.naver.com/place/1740443365</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7186,34 +7186,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>더네일</t>
+          <t>레푸스 인천영종점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>thenail_@naver.com</t>
+          <t>lje9539@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1481-0271</t>
+          <t>0507-1497-0007</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 20 215호</t>
+          <t>인천광역시 중구 영종대로 100 신성하우스빌 3층 301호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Cf_KCSIrY34/?igshid=YmMyMTA2M2Y=</t>
+          <t>https://www.instagram.com/nail_heyazi/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7243,13 +7243,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>17</v>
+        <v>172</v>
       </c>
       <c r="Q73" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="R73" t="n">
-        <v>23</v>
+        <v>222</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7258,17 +7258,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1979788121</t>
+          <t>1131150431</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979788121</t>
+          <t>https://m.place.naver.com/place/1131150431</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7280,25 +7280,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>라르떼네일</t>
+          <t>버디네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>limkyungmi10@naver.com</t>
+          <t>hhj6910@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1420-9856</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 11 해솔프라자 403-1호</t>
+          <t>인천광역시 중구 하늘중앙로195번길 21 에스디메디칼 3층 309호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rarete_nail02</t>
+          <t>https://www.instagram.com/buddy_nail__</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7333,13 +7337,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>53</v>
+        <v>621</v>
       </c>
       <c r="Q74" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>70</v>
+        <v>623</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7348,17 +7352,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1844112944</t>
+          <t>1255393282</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1844112944</t>
+          <t>https://m.place.naver.com/place/1255393282</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7370,25 +7374,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>제이네일</t>
+          <t>네일이안</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>morningapple6@naver.com</t>
+          <t>wjstngusrn@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1467-1252</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 향나무길28번길 13-1</t>
+          <t>인천광역시 중구 자연대로 47 610호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j.nail_shop</t>
+          <t>https://www.instagram.com/nail_ian</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7423,13 +7431,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="R75" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7438,17 +7446,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1237271418</t>
+          <t>1117993147</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237271418</t>
+          <t>https://m.place.naver.com/place/1117993147</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7460,29 +7468,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일 바이 담</t>
+          <t>오늘네일샵</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>11dldnjs@naver.com</t>
+          <t>webmaia21@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>032-751-6686</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 중구 햇내로13번길 17 프라임시티1차 102호 네일바이담</t>
+          <t>충청남도 서산시 대산읍 충의로 1889</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailby.dam</t>
+          <t>http://instagram.com/_nail_2day</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7517,13 +7521,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7532,17 +7536,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1880192448</t>
+          <t>1283160281</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880192448</t>
+          <t>https://m.place.naver.com/place/1283160281</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
